--- a/Error Inventory/API Error Consolidated List.xlsx
+++ b/Error Inventory/API Error Consolidated List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eagnmnwbp130a.usa.dce.usps.gov\VDIProfiles$\fsbtg0\Documents\API Consolidated file to upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{221AFA77-C70C-4A96-B5FD-8FDE26F499FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F549680-687E-456D-A4F1-C57345E92A81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="13920" firstSheet="11" activeTab="12" xr2:uid="{BD4CA92B-BD2B-408A-B66B-5389FE5197CE}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="13785" firstSheet="3" activeTab="4" xr2:uid="{BD4CA92B-BD2B-408A-B66B-5389FE5197CE}"/>
   </bookViews>
   <sheets>
     <sheet name="General Errors" sheetId="9" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4010" uniqueCount="1009">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4050" uniqueCount="1014">
   <si>
     <t>API</t>
   </si>
@@ -3118,6 +3118,21 @@
   </si>
   <si>
     <t>barcode&lt;barcode &gt;has manifested and is not eligible to be added to a SCAN Form</t>
+  </si>
+  <si>
+    <t>imageInfo.imageType, imageInfo.labelType</t>
+  </si>
+  <si>
+    <t>&lt;labelType&gt; currently does not support imageInfo.imageType of &lt;imageType&gt;</t>
+  </si>
+  <si>
+    <t>EPL format does not same page or separate page receipt functionality.</t>
+  </si>
+  <si>
+    <t>brandingImageFormat currently does not support imageInfo.imageType of 'EPL203DPI' or 'EPL300DPI'</t>
+  </si>
+  <si>
+    <t>label with trackingNumber '%s' is not eligible for containerization</t>
   </si>
 </sst>
 </file>
@@ -3261,7 +3276,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -3398,6 +3413,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Accent1" xfId="1" builtinId="29"/>
@@ -7649,7 +7667,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -8029,6 +8047,29 @@
         <v>681</v>
       </c>
     </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="10">
+        <v>400</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>957</v>
+      </c>
+      <c r="E17" s="17">
+        <v>160402</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>754</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>1013</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8039,7 +8080,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:G232"/>
+  <dimension ref="A1:G235"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
@@ -13377,6 +13418,75 @@
         <v>1002</v>
       </c>
     </row>
+    <row r="233" spans="1:7">
+      <c r="A233" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B233" s="20">
+        <v>400</v>
+      </c>
+      <c r="C233" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D233" s="21" t="s">
+        <v>959</v>
+      </c>
+      <c r="E233" s="17">
+        <v>160399</v>
+      </c>
+      <c r="F233" s="17" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G233" s="48" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" ht="30">
+      <c r="A234" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B234" s="20">
+        <v>400</v>
+      </c>
+      <c r="C234" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D234" s="21" t="s">
+        <v>959</v>
+      </c>
+      <c r="E234" s="17">
+        <v>160400</v>
+      </c>
+      <c r="F234" s="37" t="s">
+        <v>694</v>
+      </c>
+      <c r="G234" s="48" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7">
+      <c r="A235" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B235" s="20">
+        <v>400</v>
+      </c>
+      <c r="C235" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D235" s="21" t="s">
+        <v>959</v>
+      </c>
+      <c r="E235" s="17">
+        <v>160401</v>
+      </c>
+      <c r="F235" s="37" t="s">
+        <v>841</v>
+      </c>
+      <c r="G235" s="2" t="s">
+        <v>1012</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G1" xr:uid="{A36F69E6-5AC8-443F-8567-4E3FB7E927F1}"/>
   <phoneticPr fontId="9" type="noConversion"/>
@@ -13390,7 +13500,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:G191"/>
+  <dimension ref="A1:G193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
@@ -17752,6 +17862,52 @@
       </c>
       <c r="G191" s="2" t="s">
         <v>1002</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" ht="30">
+      <c r="A192" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="B192" s="21">
+        <v>400</v>
+      </c>
+      <c r="C192" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="D192" s="10" t="s">
+        <v>965</v>
+      </c>
+      <c r="E192" s="17">
+        <v>160400</v>
+      </c>
+      <c r="F192" s="33" t="s">
+        <v>694</v>
+      </c>
+      <c r="G192" s="48" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7">
+      <c r="A193" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="B193" s="21">
+        <v>400</v>
+      </c>
+      <c r="C193" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="D193" s="10" t="s">
+        <v>965</v>
+      </c>
+      <c r="E193" s="17">
+        <v>160401</v>
+      </c>
+      <c r="F193" s="33" t="s">
+        <v>841</v>
+      </c>
+      <c r="G193" s="2" t="s">
+        <v>1012</v>
       </c>
     </row>
   </sheetData>
@@ -18667,7 +18823,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -19520,6 +19676,52 @@
       </c>
       <c r="G37" s="2" t="s">
         <v>1002</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="30">
+      <c r="A38" t="s">
+        <v>475</v>
+      </c>
+      <c r="B38">
+        <v>400</v>
+      </c>
+      <c r="C38" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" t="s">
+        <v>970</v>
+      </c>
+      <c r="E38" s="26">
+        <v>160400</v>
+      </c>
+      <c r="F38" s="33" t="s">
+        <v>694</v>
+      </c>
+      <c r="G38" s="48" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
+        <v>475</v>
+      </c>
+      <c r="B39">
+        <v>400</v>
+      </c>
+      <c r="C39" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" t="s">
+        <v>970</v>
+      </c>
+      <c r="E39" s="26">
+        <v>160401</v>
+      </c>
+      <c r="F39" s="33" t="s">
+        <v>841</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>1012</v>
       </c>
     </row>
   </sheetData>
@@ -20233,6 +20435,19 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <TaxCatchAll xmlns="9cf85ca5-4acf-45da-adaa-d6bfc34b6c9f" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2595f96f-d2aa-4fa4-b5ed-10baae53ecb9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BD1EFD7F07544F4C8A5DF6ACE5557D0F" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0a46465e297c47d8b88a71685f887e65">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="2595f96f-d2aa-4fa4-b5ed-10baae53ecb9" xmlns:ns3="9cf85ca5-4acf-45da-adaa-d6bfc34b6c9f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4503a5f252426d71f93d44927b16e869" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -20478,19 +20693,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <TaxCatchAll xmlns="9cf85ca5-4acf-45da-adaa-d6bfc34b6c9f" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2595f96f-d2aa-4fa4-b5ed-10baae53ecb9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D590CCA9-7961-4660-BBC6-10104A0DDFD4}">
   <ds:schemaRefs>
@@ -20500,6 +20702,24 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3DC8D4E-C199-4BF9-AF5D-F16C7D7041E1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2595f96f-d2aa-4fa4-b5ed-10baae53ecb9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="9cf85ca5-4acf-45da-adaa-d6bfc34b6c9f"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F11AB0D6-FBA0-4F11-8778-05A9ADBB93A5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20519,24 +20739,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3DC8D4E-C199-4BF9-AF5D-F16C7D7041E1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2595f96f-d2aa-4fa4-b5ed-10baae53ecb9"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="9cf85ca5-4acf-45da-adaa-d6bfc34b6c9f"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{6c9b68e5-0371-4f27-93af-8d15f794dc29}" enabled="1" method="Privileged" siteId="{a01f407a-85cb-4a16-98bb-f28e6384bd28}" removed="0"/>

--- a/Error Inventory/API Error Consolidated List.xlsx
+++ b/Error Inventory/API Error Consolidated List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eagnmnwbp130a.usa.dce.usps.gov\VDIProfiles$\fsbtg0\Documents\API Consolidated file to upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F549680-687E-456D-A4F1-C57345E92A81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F53487B-9017-4953-8EAD-F36B8AB737A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="13785" firstSheet="3" activeTab="4" xr2:uid="{BD4CA92B-BD2B-408A-B66B-5389FE5197CE}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="13785" firstSheet="9" activeTab="10" xr2:uid="{BD4CA92B-BD2B-408A-B66B-5389FE5197CE}"/>
   </bookViews>
   <sheets>
     <sheet name="General Errors" sheetId="9" r:id="rId1"/>
@@ -23,8 +23,8 @@
     <sheet name="International Labels" sheetId="12" r:id="rId8"/>
     <sheet name="International Prices" sheetId="7" r:id="rId9"/>
     <sheet name="Location" sheetId="13" r:id="rId10"/>
-    <sheet name="Payment" sheetId="18" r:id="rId11"/>
-    <sheet name="PMOD(Open and Distribute)" sheetId="19" r:id="rId12"/>
+    <sheet name="Open and Distribute(PMOD)" sheetId="19" r:id="rId11"/>
+    <sheet name="Payment" sheetId="18" r:id="rId12"/>
     <sheet name="Scan Form" sheetId="14" r:id="rId13"/>
     <sheet name="Service Standards" sheetId="17" r:id="rId14"/>
     <sheet name="Shipping Options" sheetId="16" r:id="rId15"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4050" uniqueCount="1014">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4075" uniqueCount="1019">
   <si>
     <t>API</t>
   </si>
@@ -2715,9 +2715,6 @@
   </si>
   <si>
     <t>PMOD</t>
-  </si>
-  <si>
-    <t>destinationEntryFacilityType must be 'DESTINATION_DELIVERY_UNIT' or 'DESTINATION_SERVICE_HUB' when processingCategory is 'MIXED'</t>
   </si>
   <si>
     <t>Max image count 50 reached. Unable to upload. Images may be deleted to free space.</t>
@@ -3133,6 +3130,24 @@
   </si>
   <si>
     <t>label with trackingNumber '%s' is not eligible for containerization</t>
+  </si>
+  <si>
+    <t>We cannot create this shipment at this time. This may be due to international service disruptions. For more information on current international service disruptions, please visit https://about.usps.com/newsroom/service-alerts/international/. For product availability, please visit https://pe.usps.com/text/imm/immpg.htm.</t>
+  </si>
+  <si>
+    <t>[mailClass] is not currently available to [destination]. For supported products, please visit https://pe.usps.com/text/imm/immpg.htm.</t>
+  </si>
+  <si>
+    <t>The weight of [weight] is not supported for [destination]. The maximum weight allowed for [mailClass] to [destination] is [maxWeight]. For supported weights by country, please visit https://pe.usps.com/text/imm/immpg.htm.</t>
+  </si>
+  <si>
+    <t>[value] is not a valid [length/width/height] for [destination]. The [length/width/height] range allowed for [mailClass] to [destination] is [min] to [max]. For individual country listings and supported dimensions, please visit https://pe.usps.com/text/imm/immctry.htm.</t>
+  </si>
+  <si>
+    <t>Not eligible to use Destination Regional Processing Distribution Center when label is not mdfv8 eligible</t>
+  </si>
+  <si>
+    <t>destinationEntryFacilityType must be 'DESTINATION_DELIVERY_UNIT' when processingCategory is 'MIXED'</t>
   </si>
 </sst>
 </file>
@@ -3923,7 +3938,7 @@
         <v>18</v>
       </c>
       <c r="D2" s="35" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="E2" s="25" t="s">
         <v>525</v>
@@ -3944,7 +3959,7 @@
         <v>18</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="E3" s="25" t="s">
         <v>527</v>
@@ -3967,7 +3982,7 @@
         <v>18</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="E4" s="25" t="s">
         <v>529</v>
@@ -3990,7 +4005,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="E5" s="25" t="s">
         <v>531</v>
@@ -4013,7 +4028,7 @@
         <v>18</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="E6" s="24" t="s">
         <v>533</v>
@@ -4036,7 +4051,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="E7" s="24" t="s">
         <v>535</v>
@@ -4059,7 +4074,7 @@
         <v>18</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="E8" s="24" t="s">
         <v>537</v>
@@ -4082,7 +4097,7 @@
         <v>18</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="E9" s="24" t="s">
         <v>539</v>
@@ -4105,7 +4120,7 @@
         <v>18</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="E10" s="24" t="s">
         <v>541</v>
@@ -4123,6 +4138,465 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C1B7C1-6FF6-49B7-8FF7-3B1E3D2E2BE9}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="66.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
+    <col min="7" max="7" width="126" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="35.25" customHeight="1">
+      <c r="A2" s="10" t="s">
+        <v>882</v>
+      </c>
+      <c r="B2" s="10">
+        <v>400</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>849</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="10" t="s">
+        <v>882</v>
+      </c>
+      <c r="B3" s="10">
+        <v>400</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="E3" s="24">
+        <v>160299</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>851</v>
+      </c>
+      <c r="G3" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="10" t="s">
+        <v>882</v>
+      </c>
+      <c r="B4" s="10">
+        <v>400</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>975</v>
+      </c>
+      <c r="E4" s="17">
+        <v>160321</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>852</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="30">
+      <c r="A5" s="10" t="s">
+        <v>882</v>
+      </c>
+      <c r="B5" s="10">
+        <v>400</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>806</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="10" t="s">
+        <v>882</v>
+      </c>
+      <c r="B6" s="10">
+        <v>400</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>977</v>
+      </c>
+      <c r="E6" s="17">
+        <v>160344</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>909</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="10" t="s">
+        <v>882</v>
+      </c>
+      <c r="B7" s="10">
+        <v>400</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>977</v>
+      </c>
+      <c r="E7" s="17">
+        <v>160345</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>909</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="10" t="s">
+        <v>882</v>
+      </c>
+      <c r="B8" s="10">
+        <v>400</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="E8" s="17">
+        <v>160350</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>908</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="10" t="s">
+        <v>882</v>
+      </c>
+      <c r="B9" s="10">
+        <v>400</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="E9" s="17">
+        <v>160352</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>908</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="10" t="s">
+        <v>882</v>
+      </c>
+      <c r="B10" s="10">
+        <v>400</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="E10" s="17">
+        <v>160353</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>908</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="10" t="s">
+        <v>882</v>
+      </c>
+      <c r="B11" s="10">
+        <v>400</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="E11" s="17">
+        <v>160354</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>908</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="10" t="s">
+        <v>882</v>
+      </c>
+      <c r="B12" s="10">
+        <v>400</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="E12" s="17">
+        <v>160355</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>908</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="10" t="s">
+        <v>882</v>
+      </c>
+      <c r="B13" s="10">
+        <v>400</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="E13" s="17">
+        <v>160371</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>932</v>
+      </c>
+      <c r="G13" s="46" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="10" t="s">
+        <v>882</v>
+      </c>
+      <c r="B14" s="10">
+        <v>400</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="E14" s="17">
+        <v>160373</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>764</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="45">
+      <c r="A15" s="10" t="s">
+        <v>882</v>
+      </c>
+      <c r="B15" s="10">
+        <v>400</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="E15" s="17">
+        <v>160374</v>
+      </c>
+      <c r="F15" s="33" t="s">
+        <v>933</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="30">
+      <c r="A16" s="10" t="s">
+        <v>882</v>
+      </c>
+      <c r="B16" s="10">
+        <v>400</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="E16" s="17">
+        <v>160385</v>
+      </c>
+      <c r="F16" s="33" t="s">
+        <v>994</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="30">
+      <c r="A17" s="10" t="s">
+        <v>882</v>
+      </c>
+      <c r="B17" s="10">
+        <v>400</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="E17" s="17">
+        <v>160386</v>
+      </c>
+      <c r="F17" s="33" t="s">
+        <v>994</v>
+      </c>
+      <c r="G17" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="30">
+      <c r="A18" s="10" t="s">
+        <v>882</v>
+      </c>
+      <c r="B18" s="10">
+        <v>400</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="E18" s="17">
+        <v>160387</v>
+      </c>
+      <c r="F18" s="33" t="s">
+        <v>908</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="10" t="s">
+        <v>882</v>
+      </c>
+      <c r="B19" s="10">
+        <v>400</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="E19" s="17">
+        <v>160403</v>
+      </c>
+      <c r="F19" t="s">
+        <v>840</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4D80F6E-C307-4E44-B167-F39BBE855D2F}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -4172,7 +4646,7 @@
         <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="E2" s="24" t="s">
         <v>544</v>
@@ -4195,7 +4669,7 @@
         <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E3" s="24" t="s">
         <v>546</v>
@@ -4218,7 +4692,7 @@
         <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E4" s="24" t="s">
         <v>548</v>
@@ -4241,7 +4715,7 @@
         <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E5" s="24" t="s">
         <v>550</v>
@@ -4264,7 +4738,7 @@
         <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E6" s="24" t="s">
         <v>552</v>
@@ -4287,7 +4761,7 @@
         <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E7" s="24" t="s">
         <v>554</v>
@@ -4310,7 +4784,7 @@
         <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E8" s="24" t="s">
         <v>556</v>
@@ -4333,7 +4807,7 @@
         <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E9" s="24" t="s">
         <v>558</v>
@@ -4356,7 +4830,7 @@
         <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E10" s="24" t="s">
         <v>560</v>
@@ -4379,7 +4853,7 @@
         <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E11" s="24" t="s">
         <v>562</v>
@@ -4402,7 +4876,7 @@
         <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E12" s="24" t="s">
         <v>564</v>
@@ -4425,7 +4899,7 @@
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E13" s="24" t="s">
         <v>566</v>
@@ -4448,7 +4922,7 @@
         <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E14" s="24" t="s">
         <v>568</v>
@@ -4471,7 +4945,7 @@
         <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E15" s="24" t="s">
         <v>570</v>
@@ -4494,7 +4968,7 @@
         <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E16" s="24">
         <v>160289</v>
@@ -4517,7 +4991,7 @@
         <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E17" s="24">
         <v>160290</v>
@@ -4540,16 +5014,16 @@
         <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>802</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -4563,16 +5037,16 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="F19" s="17" t="s">
         <v>834</v>
       </c>
       <c r="G19" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -4586,16 +5060,16 @@
         <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="F20" s="17" t="s">
         <v>834</v>
       </c>
       <c r="G20" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -4609,16 +5083,16 @@
         <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="F21" s="17" t="s">
         <v>834</v>
       </c>
       <c r="G21" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -4632,16 +5106,16 @@
         <v>18</v>
       </c>
       <c r="D22" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="F22" s="17" t="s">
         <v>834</v>
       </c>
       <c r="G22" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -4655,16 +5129,16 @@
         <v>18</v>
       </c>
       <c r="D23" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="F23" s="17" t="s">
         <v>834</v>
       </c>
       <c r="G23" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -4678,16 +5152,16 @@
         <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="F24" s="17" t="s">
         <v>834</v>
       </c>
       <c r="G24" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -4701,7 +5175,7 @@
         <v>18</v>
       </c>
       <c r="D25" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E25" s="24">
         <v>100007</v>
@@ -4710,7 +5184,7 @@
         <v>834</v>
       </c>
       <c r="G25" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -4724,7 +5198,7 @@
         <v>18</v>
       </c>
       <c r="D26" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E26" s="24">
         <v>160390</v>
@@ -4733,442 +5207,6 @@
         <v>834</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>999</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C1B7C1-6FF6-49B7-8FF7-3B1E3D2E2BE9}">
-  <sheetPr>
-    <tabColor rgb="FF92D050"/>
-  </sheetPr>
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="66.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" customWidth="1"/>
-    <col min="7" max="7" width="126" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="35.25" customHeight="1">
-      <c r="A2" s="10" t="s">
-        <v>882</v>
-      </c>
-      <c r="B2" s="10">
-        <v>400</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>976</v>
-      </c>
-      <c r="E2" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="F2" s="33" t="s">
-        <v>849</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="10" t="s">
-        <v>882</v>
-      </c>
-      <c r="B3" s="10">
-        <v>400</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>976</v>
-      </c>
-      <c r="E3" s="24">
-        <v>160299</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>851</v>
-      </c>
-      <c r="G3" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="10" t="s">
-        <v>882</v>
-      </c>
-      <c r="B4" s="10">
-        <v>400</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>976</v>
-      </c>
-      <c r="E4" s="17">
-        <v>160321</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>852</v>
-      </c>
-      <c r="G4" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="30">
-      <c r="A5" s="10" t="s">
-        <v>882</v>
-      </c>
-      <c r="B5" s="10">
-        <v>400</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>977</v>
-      </c>
-      <c r="E5" s="24" t="s">
-        <v>210</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>806</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="10" t="s">
-        <v>882</v>
-      </c>
-      <c r="B6" s="10">
-        <v>400</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>978</v>
-      </c>
-      <c r="E6" s="17">
-        <v>160344</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>910</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="10" t="s">
-        <v>882</v>
-      </c>
-      <c r="B7" s="10">
-        <v>400</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" t="s">
-        <v>978</v>
-      </c>
-      <c r="E7" s="17">
-        <v>160345</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>910</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="10" t="s">
-        <v>882</v>
-      </c>
-      <c r="B8" s="10">
-        <v>400</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>976</v>
-      </c>
-      <c r="E8" s="17">
-        <v>160350</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>909</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="10" t="s">
-        <v>882</v>
-      </c>
-      <c r="B9" s="10">
-        <v>400</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>976</v>
-      </c>
-      <c r="E9" s="17">
-        <v>160352</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>909</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="10" t="s">
-        <v>882</v>
-      </c>
-      <c r="B10" s="10">
-        <v>400</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>976</v>
-      </c>
-      <c r="E10" s="17">
-        <v>160353</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>909</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="10" t="s">
-        <v>882</v>
-      </c>
-      <c r="B11" s="10">
-        <v>400</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>976</v>
-      </c>
-      <c r="E11" s="17">
-        <v>160354</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>909</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="10" t="s">
-        <v>882</v>
-      </c>
-      <c r="B12" s="10">
-        <v>400</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>976</v>
-      </c>
-      <c r="E12" s="17">
-        <v>160355</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>909</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="10" t="s">
-        <v>882</v>
-      </c>
-      <c r="B13" s="10">
-        <v>400</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>976</v>
-      </c>
-      <c r="E13" s="17">
-        <v>160371</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>933</v>
-      </c>
-      <c r="G13" s="46" t="s">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="10" t="s">
-        <v>882</v>
-      </c>
-      <c r="B14" s="10">
-        <v>400</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>976</v>
-      </c>
-      <c r="E14" s="17">
-        <v>160373</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>764</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="45">
-      <c r="A15" s="10" t="s">
-        <v>882</v>
-      </c>
-      <c r="B15" s="10">
-        <v>400</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>976</v>
-      </c>
-      <c r="E15" s="17">
-        <v>160374</v>
-      </c>
-      <c r="F15" s="33" t="s">
-        <v>934</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>937</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="30">
-      <c r="A16" s="10" t="s">
-        <v>882</v>
-      </c>
-      <c r="B16" s="10">
-        <v>400</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>976</v>
-      </c>
-      <c r="E16" s="17">
-        <v>160385</v>
-      </c>
-      <c r="F16" s="33" t="s">
-        <v>995</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="30">
-      <c r="A17" s="10" t="s">
-        <v>882</v>
-      </c>
-      <c r="B17" s="10">
-        <v>400</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>976</v>
-      </c>
-      <c r="E17" s="17">
-        <v>160386</v>
-      </c>
-      <c r="F17" s="33" t="s">
-        <v>995</v>
-      </c>
-      <c r="G17" t="s">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="30">
-      <c r="A18" s="10" t="s">
-        <v>882</v>
-      </c>
-      <c r="B18" s="10">
-        <v>400</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>976</v>
-      </c>
-      <c r="E18" s="17">
-        <v>160387</v>
-      </c>
-      <c r="F18" s="33" t="s">
-        <v>909</v>
-      </c>
-      <c r="G18" s="2" t="s">
         <v>998</v>
       </c>
     </row>
@@ -5228,7 +5266,7 @@
         <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E2" s="25" t="s">
         <v>573</v>
@@ -5251,7 +5289,7 @@
         <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E3" s="25" t="s">
         <v>575</v>
@@ -5272,7 +5310,7 @@
         <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E4" s="25" t="s">
         <v>577</v>
@@ -5295,7 +5333,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E5" s="25" t="s">
         <v>579</v>
@@ -5318,7 +5356,7 @@
         <v>18</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E6" s="25" t="s">
         <v>581</v>
@@ -5341,7 +5379,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E7" s="25" t="s">
         <v>583</v>
@@ -5364,7 +5402,7 @@
         <v>18</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E8" s="17" t="s">
         <v>585</v>
@@ -5387,7 +5425,7 @@
         <v>18</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E9" s="17" t="s">
         <v>587</v>
@@ -5410,7 +5448,7 @@
         <v>18</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E10" s="17" t="s">
         <v>589</v>
@@ -5433,7 +5471,7 @@
         <v>18</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E11" s="17" t="s">
         <v>591</v>
@@ -5456,7 +5494,7 @@
         <v>18</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E12" s="17" t="s">
         <v>593</v>
@@ -5479,7 +5517,7 @@
         <v>18</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E13" s="17" t="s">
         <v>595</v>
@@ -5502,7 +5540,7 @@
         <v>18</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>597</v>
@@ -5525,7 +5563,7 @@
         <v>18</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E15" s="17" t="s">
         <v>599</v>
@@ -5548,7 +5586,7 @@
         <v>18</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>601</v>
@@ -5571,7 +5609,7 @@
         <v>18</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E17" s="24">
         <v>160397</v>
@@ -5580,7 +5618,7 @@
         <v>756</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -5594,7 +5632,7 @@
         <v>18</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E18" s="24">
         <v>160398</v>
@@ -5603,7 +5641,7 @@
         <v>756</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
   </sheetData>
@@ -5662,7 +5700,7 @@
         <v>18</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="E2" s="24" t="s">
         <v>605</v>
@@ -5685,7 +5723,7 @@
         <v>18</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="E3" s="24" t="s">
         <v>607</v>
@@ -5708,7 +5746,7 @@
         <v>18</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="E4" s="26">
         <v>160288</v>
@@ -5776,7 +5814,7 @@
         <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E2" s="29" t="s">
         <v>416</v>
@@ -5797,7 +5835,7 @@
         <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E3" s="29" t="s">
         <v>89</v>
@@ -5818,7 +5856,7 @@
         <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E4" s="29" t="s">
         <v>418</v>
@@ -5839,7 +5877,7 @@
         <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E5" s="29" t="s">
         <v>420</v>
@@ -5860,7 +5898,7 @@
         <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E6" s="29" t="s">
         <v>424</v>
@@ -5881,7 +5919,7 @@
         <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E7" s="29" t="s">
         <v>427</v>
@@ -5902,7 +5940,7 @@
         <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E8" s="29" t="s">
         <v>422</v>
@@ -5923,7 +5961,7 @@
         <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E9" s="29" t="s">
         <v>130</v>
@@ -5944,7 +5982,7 @@
         <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E10" s="29" t="s">
         <v>440</v>
@@ -5965,7 +6003,7 @@
         <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E11" s="29" t="s">
         <v>442</v>
@@ -5986,7 +6024,7 @@
         <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E12" s="29" t="s">
         <v>444</v>
@@ -6007,7 +6045,7 @@
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E13" s="29" t="s">
         <v>446</v>
@@ -6028,7 +6066,7 @@
         <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E14" s="29" t="s">
         <v>448</v>
@@ -6049,7 +6087,7 @@
         <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E15" s="29" t="s">
         <v>450</v>
@@ -6070,7 +6108,7 @@
         <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E16" s="29" t="s">
         <v>452</v>
@@ -6091,7 +6129,7 @@
         <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E17" s="29" t="s">
         <v>454</v>
@@ -6112,7 +6150,7 @@
         <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E18" s="29" t="s">
         <v>456</v>
@@ -6133,7 +6171,7 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E19" s="29" t="s">
         <v>458</v>
@@ -6154,7 +6192,7 @@
         <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E20" s="29" t="s">
         <v>459</v>
@@ -6175,7 +6213,7 @@
         <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E21" s="29" t="s">
         <v>461</v>
@@ -6196,7 +6234,7 @@
         <v>18</v>
       </c>
       <c r="D22" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E22" s="25" t="s">
         <v>605</v>
@@ -6217,7 +6255,7 @@
         <v>18</v>
       </c>
       <c r="D23" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E23" s="25" t="s">
         <v>607</v>
@@ -6238,7 +6276,7 @@
         <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E24" s="27" t="s">
         <v>19</v>
@@ -6259,7 +6297,7 @@
         <v>18</v>
       </c>
       <c r="D25" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E25" s="27" t="s">
         <v>21</v>
@@ -6280,7 +6318,7 @@
         <v>18</v>
       </c>
       <c r="D26" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E26" s="27" t="s">
         <v>23</v>
@@ -6301,7 +6339,7 @@
         <v>18</v>
       </c>
       <c r="D27" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E27" s="27" t="s">
         <v>25</v>
@@ -6322,7 +6360,7 @@
         <v>18</v>
       </c>
       <c r="D28" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E28" s="27" t="s">
         <v>27</v>
@@ -6343,7 +6381,7 @@
         <v>18</v>
       </c>
       <c r="D29" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E29" s="27" t="s">
         <v>29</v>
@@ -6364,7 +6402,7 @@
         <v>18</v>
       </c>
       <c r="D30" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E30" s="24" t="s">
         <v>613</v>
@@ -6387,7 +6425,7 @@
         <v>18</v>
       </c>
       <c r="D31" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E31" s="24" t="s">
         <v>615</v>
@@ -6410,7 +6448,7 @@
         <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E32" s="24" t="s">
         <v>617</v>
@@ -6433,7 +6471,7 @@
         <v>18</v>
       </c>
       <c r="D33" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E33" s="24" t="s">
         <v>619</v>
@@ -6456,7 +6494,7 @@
         <v>18</v>
       </c>
       <c r="D34" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E34" s="24" t="s">
         <v>620</v>
@@ -6479,7 +6517,7 @@
         <v>18</v>
       </c>
       <c r="D35" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E35" s="24" t="s">
         <v>622</v>
@@ -6502,7 +6540,7 @@
         <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E36" s="24" t="s">
         <v>624</v>
@@ -6525,7 +6563,7 @@
         <v>18</v>
       </c>
       <c r="D37" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E37" s="24" t="s">
         <v>625</v>
@@ -6548,7 +6586,7 @@
         <v>18</v>
       </c>
       <c r="D38" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E38" s="24" t="s">
         <v>626</v>
@@ -6571,7 +6609,7 @@
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E39" s="24" t="s">
         <v>628</v>
@@ -6594,7 +6632,7 @@
         <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E40" s="17">
         <v>160391</v>
@@ -6603,7 +6641,7 @@
         <v>710</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -6617,7 +6655,7 @@
         <v>18</v>
       </c>
       <c r="D41" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E41" s="24">
         <v>160392</v>
@@ -6626,7 +6664,7 @@
         <v>710</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
   </sheetData>
@@ -6685,7 +6723,7 @@
         <v>18</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E2" s="25" t="s">
         <v>631</v>
@@ -6706,7 +6744,7 @@
         <v>18</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E3" s="25" t="s">
         <v>633</v>
@@ -6727,7 +6765,7 @@
         <v>18</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E4" s="25" t="s">
         <v>635</v>
@@ -6748,7 +6786,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E5" s="25" t="s">
         <v>637</v>
@@ -6769,7 +6807,7 @@
         <v>18</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E6" s="29" t="s">
         <v>639</v>
@@ -6790,7 +6828,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E7" s="25" t="s">
         <v>641</v>
@@ -6811,7 +6849,7 @@
         <v>18</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E8" s="25" t="s">
         <v>643</v>
@@ -6832,7 +6870,7 @@
         <v>18</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E9" s="25" t="s">
         <v>645</v>
@@ -6853,7 +6891,7 @@
         <v>18</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E10" s="25" t="s">
         <v>647</v>
@@ -6874,7 +6912,7 @@
         <v>18</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E11" s="25" t="s">
         <v>649</v>
@@ -6895,7 +6933,7 @@
         <v>18</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E12" s="25" t="s">
         <v>651</v>
@@ -6916,7 +6954,7 @@
         <v>18</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E13" s="25" t="s">
         <v>653</v>
@@ -6937,7 +6975,7 @@
         <v>18</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E14" s="25" t="s">
         <v>655</v>
@@ -7005,7 +7043,7 @@
         <v>18</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E2" s="27" t="s">
         <v>19</v>
@@ -7028,7 +7066,7 @@
         <v>18</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E3" s="27" t="s">
         <v>21</v>
@@ -7051,7 +7089,7 @@
         <v>18</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E4" s="27" t="s">
         <v>23</v>
@@ -7074,7 +7112,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E5" s="27" t="s">
         <v>25</v>
@@ -7097,7 +7135,7 @@
         <v>18</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E6" s="27" t="s">
         <v>27</v>
@@ -7120,7 +7158,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E7" s="27" t="s">
         <v>29</v>
@@ -7224,7 +7262,7 @@
         <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E2" s="28" t="s">
         <v>32</v>
@@ -7245,7 +7283,7 @@
         <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E3" s="28" t="s">
         <v>34</v>
@@ -7266,7 +7304,7 @@
         <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E4" s="28" t="s">
         <v>36</v>
@@ -7287,7 +7325,7 @@
         <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E5" s="28" t="s">
         <v>38</v>
@@ -7308,7 +7346,7 @@
         <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E6" s="28" t="s">
         <v>40</v>
@@ -7329,7 +7367,7 @@
         <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E7" s="28" t="s">
         <v>42</v>
@@ -7350,7 +7388,7 @@
         <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E8" s="28" t="s">
         <v>44</v>
@@ -7371,7 +7409,7 @@
         <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E9" s="28" t="s">
         <v>46</v>
@@ -7392,7 +7430,7 @@
         <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E10" s="28" t="s">
         <v>48</v>
@@ -7413,7 +7451,7 @@
         <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E11" s="28" t="s">
         <v>50</v>
@@ -7434,7 +7472,7 @@
         <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E12" s="28" t="s">
         <v>52</v>
@@ -7455,7 +7493,7 @@
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E13" s="28" t="s">
         <v>54</v>
@@ -7476,7 +7514,7 @@
         <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E14" s="28" t="s">
         <v>56</v>
@@ -7497,7 +7535,7 @@
         <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E15" s="28" t="s">
         <v>58</v>
@@ -7518,7 +7556,7 @@
         <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E16" s="28" t="s">
         <v>60</v>
@@ -7539,7 +7577,7 @@
         <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E17" s="28" t="s">
         <v>61</v>
@@ -7560,7 +7598,7 @@
         <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E18" s="28" t="s">
         <v>62</v>
@@ -7581,7 +7619,7 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E19" s="28" t="s">
         <v>63</v>
@@ -7602,7 +7640,7 @@
         <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E20" s="28" t="s">
         <v>64</v>
@@ -7623,7 +7661,7 @@
         <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E21" s="28" t="s">
         <v>65</v>
@@ -7644,7 +7682,7 @@
         <v>18</v>
       </c>
       <c r="D22" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E22" s="28" t="s">
         <v>66</v>
@@ -7713,7 +7751,7 @@
         <v>18</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E2" s="25" t="s">
         <v>69</v>
@@ -7736,7 +7774,7 @@
         <v>18</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E3" s="25" t="s">
         <v>71</v>
@@ -7759,7 +7797,7 @@
         <v>18</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E4" s="25" t="s">
         <v>73</v>
@@ -7782,7 +7820,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E5" s="25" t="s">
         <v>75</v>
@@ -7805,7 +7843,7 @@
         <v>18</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E6" s="25" t="s">
         <v>77</v>
@@ -7828,7 +7866,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E7" s="25" t="s">
         <v>79</v>
@@ -7851,7 +7889,7 @@
         <v>18</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E8" s="25" t="s">
         <v>81</v>
@@ -7874,7 +7912,7 @@
         <v>18</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E9" s="25" t="s">
         <v>83</v>
@@ -7897,7 +7935,7 @@
         <v>18</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="E10" s="25" t="s">
         <v>85</v>
@@ -7920,7 +7958,7 @@
         <v>18</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E11" s="25" t="s">
         <v>853</v>
@@ -7943,7 +7981,7 @@
         <v>18</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E12" s="24">
         <v>160295</v>
@@ -7966,7 +8004,7 @@
         <v>18</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E13" s="24">
         <v>160296</v>
@@ -7989,7 +8027,7 @@
         <v>18</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E14" s="24">
         <v>160297</v>
@@ -8012,7 +8050,7 @@
         <v>18</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E15" s="24">
         <v>160298</v>
@@ -8035,7 +8073,7 @@
         <v>18</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E16" s="24">
         <v>160299</v>
@@ -8058,7 +8096,7 @@
         <v>18</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E17" s="17">
         <v>160402</v>
@@ -8067,7 +8105,7 @@
         <v>754</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
   </sheetData>
@@ -8126,7 +8164,7 @@
         <v>18</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E2" s="25">
         <v>160001</v>
@@ -8149,7 +8187,7 @@
         <v>18</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E3" s="25" t="s">
         <v>89</v>
@@ -8172,7 +8210,7 @@
         <v>18</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E4" s="25">
         <v>160003</v>
@@ -8195,7 +8233,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E5" s="25">
         <v>160004</v>
@@ -8218,7 +8256,7 @@
         <v>18</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E6" s="25">
         <v>160005</v>
@@ -8241,7 +8279,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E7" s="25" t="s">
         <v>94</v>
@@ -8264,7 +8302,7 @@
         <v>18</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E8" s="25" t="s">
         <v>96</v>
@@ -8287,7 +8325,7 @@
         <v>18</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E9" s="25" t="s">
         <v>98</v>
@@ -8310,7 +8348,7 @@
         <v>18</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E10" s="25">
         <v>160010</v>
@@ -8333,7 +8371,7 @@
         <v>18</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E11" s="25" t="s">
         <v>101</v>
@@ -8356,7 +8394,7 @@
         <v>18</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E12" s="25" t="s">
         <v>103</v>
@@ -8379,7 +8417,7 @@
         <v>18</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E13" s="25" t="s">
         <v>105</v>
@@ -8402,7 +8440,7 @@
         <v>18</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E14" s="25" t="s">
         <v>107</v>
@@ -8425,7 +8463,7 @@
         <v>18</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E15" s="25" t="s">
         <v>109</v>
@@ -8448,7 +8486,7 @@
         <v>18</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E16" s="25" t="s">
         <v>107</v>
@@ -8471,7 +8509,7 @@
         <v>18</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E17" s="25" t="s">
         <v>112</v>
@@ -8494,7 +8532,7 @@
         <v>18</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E18" s="25" t="s">
         <v>109</v>
@@ -8517,7 +8555,7 @@
         <v>18</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E19" s="25" t="s">
         <v>109</v>
@@ -8540,7 +8578,7 @@
         <v>18</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E20" s="25" t="s">
         <v>116</v>
@@ -8563,7 +8601,7 @@
         <v>18</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E21" s="25" t="s">
         <v>118</v>
@@ -8586,7 +8624,7 @@
         <v>18</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E22" s="25" t="s">
         <v>120</v>
@@ -8609,7 +8647,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E23" s="25" t="s">
         <v>122</v>
@@ -8632,7 +8670,7 @@
         <v>18</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E24" s="25" t="s">
         <v>124</v>
@@ -8655,7 +8693,7 @@
         <v>18</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E25" s="25" t="s">
         <v>126</v>
@@ -8678,7 +8716,7 @@
         <v>18</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E26" s="24" t="s">
         <v>128</v>
@@ -8701,7 +8739,7 @@
         <v>18</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E27" s="24" t="s">
         <v>130</v>
@@ -8724,7 +8762,7 @@
         <v>18</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E28" s="24" t="s">
         <v>132</v>
@@ -8747,7 +8785,7 @@
         <v>18</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E29" s="24" t="s">
         <v>134</v>
@@ -8770,7 +8808,7 @@
         <v>18</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E30" s="26" t="s">
         <v>136</v>
@@ -8793,7 +8831,7 @@
         <v>18</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E31" s="26" t="s">
         <v>138</v>
@@ -8816,7 +8854,7 @@
         <v>18</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E32" s="26" t="s">
         <v>140</v>
@@ -8839,7 +8877,7 @@
         <v>18</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E33" s="26" t="s">
         <v>142</v>
@@ -8862,7 +8900,7 @@
         <v>18</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E34" s="26" t="s">
         <v>144</v>
@@ -8885,7 +8923,7 @@
         <v>18</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E35" s="26" t="s">
         <v>146</v>
@@ -8908,7 +8946,7 @@
         <v>18</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E36" s="26" t="s">
         <v>148</v>
@@ -8931,7 +8969,7 @@
         <v>18</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E37" s="24" t="s">
         <v>150</v>
@@ -8954,7 +8992,7 @@
         <v>18</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E38" s="24" t="s">
         <v>152</v>
@@ -8977,7 +9015,7 @@
         <v>18</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E39" s="24" t="s">
         <v>154</v>
@@ -9000,7 +9038,7 @@
         <v>18</v>
       </c>
       <c r="D40" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E40" s="24" t="s">
         <v>156</v>
@@ -9023,7 +9061,7 @@
         <v>18</v>
       </c>
       <c r="D41" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E41" s="24" t="s">
         <v>157</v>
@@ -9046,7 +9084,7 @@
         <v>18</v>
       </c>
       <c r="D42" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E42" s="17" t="s">
         <v>158</v>
@@ -9069,7 +9107,7 @@
         <v>18</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E43" s="17" t="s">
         <v>160</v>
@@ -9092,7 +9130,7 @@
         <v>18</v>
       </c>
       <c r="D44" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E44" s="17" t="s">
         <v>162</v>
@@ -9115,7 +9153,7 @@
         <v>18</v>
       </c>
       <c r="D45" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E45" s="17" t="s">
         <v>164</v>
@@ -9138,7 +9176,7 @@
         <v>18</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E46" s="17" t="s">
         <v>166</v>
@@ -9161,7 +9199,7 @@
         <v>18</v>
       </c>
       <c r="D47" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E47" s="17" t="s">
         <v>168</v>
@@ -9184,7 +9222,7 @@
         <v>18</v>
       </c>
       <c r="D48" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E48" s="17" t="s">
         <v>170</v>
@@ -9207,7 +9245,7 @@
         <v>18</v>
       </c>
       <c r="D49" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E49" s="17" t="s">
         <v>172</v>
@@ -9230,7 +9268,7 @@
         <v>18</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E50" s="17" t="s">
         <v>174</v>
@@ -9253,7 +9291,7 @@
         <v>18</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E51" s="17" t="s">
         <v>176</v>
@@ -9276,7 +9314,7 @@
         <v>18</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E52" s="17" t="s">
         <v>178</v>
@@ -9299,7 +9337,7 @@
         <v>18</v>
       </c>
       <c r="D53" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E53" s="17" t="s">
         <v>180</v>
@@ -9322,7 +9360,7 @@
         <v>18</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E54" s="17" t="s">
         <v>182</v>
@@ -9345,7 +9383,7 @@
         <v>18</v>
       </c>
       <c r="D55" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E55" s="17" t="s">
         <v>184</v>
@@ -9368,7 +9406,7 @@
         <v>18</v>
       </c>
       <c r="D56" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E56" s="17" t="s">
         <v>186</v>
@@ -9391,7 +9429,7 @@
         <v>18</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E57" s="17" t="s">
         <v>187</v>
@@ -9414,7 +9452,7 @@
         <v>18</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E58" s="17" t="s">
         <v>189</v>
@@ -9437,7 +9475,7 @@
         <v>18</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E59" s="17" t="s">
         <v>191</v>
@@ -9460,7 +9498,7 @@
         <v>18</v>
       </c>
       <c r="D60" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E60" s="17" t="s">
         <v>192</v>
@@ -9483,7 +9521,7 @@
         <v>18</v>
       </c>
       <c r="D61" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E61" s="17" t="s">
         <v>193</v>
@@ -9506,7 +9544,7 @@
         <v>18</v>
       </c>
       <c r="D62" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E62" s="17" t="s">
         <v>194</v>
@@ -9529,7 +9567,7 @@
         <v>18</v>
       </c>
       <c r="D63" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E63" s="17" t="s">
         <v>196</v>
@@ -9552,7 +9590,7 @@
         <v>18</v>
       </c>
       <c r="D64" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E64" s="17" t="s">
         <v>197</v>
@@ -9575,7 +9613,7 @@
         <v>18</v>
       </c>
       <c r="D65" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E65" s="17" t="s">
         <v>199</v>
@@ -9598,7 +9636,7 @@
         <v>18</v>
       </c>
       <c r="D66" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E66" s="17" t="s">
         <v>201</v>
@@ -9621,7 +9659,7 @@
         <v>18</v>
       </c>
       <c r="D67" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E67" s="17" t="s">
         <v>202</v>
@@ -9644,7 +9682,7 @@
         <v>18</v>
       </c>
       <c r="D68" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E68" s="17" t="s">
         <v>204</v>
@@ -9667,7 +9705,7 @@
         <v>18</v>
       </c>
       <c r="D69" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E69" s="17" t="s">
         <v>206</v>
@@ -9690,7 +9728,7 @@
         <v>18</v>
       </c>
       <c r="D70" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E70" s="17" t="s">
         <v>208</v>
@@ -9713,7 +9751,7 @@
         <v>18</v>
       </c>
       <c r="D71" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E71" s="17" t="s">
         <v>210</v>
@@ -9736,7 +9774,7 @@
         <v>18</v>
       </c>
       <c r="D72" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E72" s="17" t="s">
         <v>212</v>
@@ -9759,7 +9797,7 @@
         <v>18</v>
       </c>
       <c r="D73" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E73" s="17" t="s">
         <v>214</v>
@@ -9782,7 +9820,7 @@
         <v>18</v>
       </c>
       <c r="D74" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E74" s="17" t="s">
         <v>216</v>
@@ -9805,7 +9843,7 @@
         <v>18</v>
       </c>
       <c r="D75" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E75" s="17" t="s">
         <v>218</v>
@@ -9828,7 +9866,7 @@
         <v>18</v>
       </c>
       <c r="D76" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E76" s="17" t="s">
         <v>220</v>
@@ -9851,7 +9889,7 @@
         <v>18</v>
       </c>
       <c r="D77" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E77" s="17" t="s">
         <v>222</v>
@@ -9874,7 +9912,7 @@
         <v>18</v>
       </c>
       <c r="D78" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E78" s="17" t="s">
         <v>224</v>
@@ -9897,7 +9935,7 @@
         <v>18</v>
       </c>
       <c r="D79" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E79" s="17" t="s">
         <v>226</v>
@@ -9920,7 +9958,7 @@
         <v>18</v>
       </c>
       <c r="D80" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E80" s="17" t="s">
         <v>228</v>
@@ -9943,7 +9981,7 @@
         <v>18</v>
       </c>
       <c r="D81" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E81" s="17" t="s">
         <v>230</v>
@@ -9966,7 +10004,7 @@
         <v>18</v>
       </c>
       <c r="D82" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E82" s="17" t="s">
         <v>232</v>
@@ -9989,7 +10027,7 @@
         <v>18</v>
       </c>
       <c r="D83" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E83" s="17" t="s">
         <v>234</v>
@@ -10012,7 +10050,7 @@
         <v>18</v>
       </c>
       <c r="D84" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E84" s="17" t="s">
         <v>236</v>
@@ -10035,7 +10073,7 @@
         <v>18</v>
       </c>
       <c r="D85" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E85" s="17" t="s">
         <v>238</v>
@@ -10058,7 +10096,7 @@
         <v>18</v>
       </c>
       <c r="D86" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E86" s="17" t="s">
         <v>240</v>
@@ -10081,7 +10119,7 @@
         <v>18</v>
       </c>
       <c r="D87" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E87" s="17" t="s">
         <v>242</v>
@@ -10104,7 +10142,7 @@
         <v>18</v>
       </c>
       <c r="D88" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E88" s="17" t="s">
         <v>244</v>
@@ -10127,7 +10165,7 @@
         <v>18</v>
       </c>
       <c r="D89" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E89" s="17" t="s">
         <v>246</v>
@@ -10150,7 +10188,7 @@
         <v>18</v>
       </c>
       <c r="D90" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E90" s="17" t="s">
         <v>247</v>
@@ -10173,7 +10211,7 @@
         <v>18</v>
       </c>
       <c r="D91" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E91" s="17" t="s">
         <v>249</v>
@@ -10196,7 +10234,7 @@
         <v>18</v>
       </c>
       <c r="D92" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E92" s="17" t="s">
         <v>251</v>
@@ -10219,7 +10257,7 @@
         <v>18</v>
       </c>
       <c r="D93" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E93" s="17" t="s">
         <v>253</v>
@@ -10242,7 +10280,7 @@
         <v>18</v>
       </c>
       <c r="D94" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E94" s="17" t="s">
         <v>254</v>
@@ -10265,7 +10303,7 @@
         <v>18</v>
       </c>
       <c r="D95" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E95" s="17" t="s">
         <v>255</v>
@@ -10288,7 +10326,7 @@
         <v>18</v>
       </c>
       <c r="D96" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E96" s="17" t="s">
         <v>256</v>
@@ -10311,7 +10349,7 @@
         <v>18</v>
       </c>
       <c r="D97" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E97" s="17" t="s">
         <v>258</v>
@@ -10334,7 +10372,7 @@
         <v>18</v>
       </c>
       <c r="D98" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E98" s="17" t="s">
         <v>260</v>
@@ -10357,7 +10395,7 @@
         <v>18</v>
       </c>
       <c r="D99" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E99" s="17" t="s">
         <v>262</v>
@@ -10380,7 +10418,7 @@
         <v>18</v>
       </c>
       <c r="D100" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E100" s="17" t="s">
         <v>264</v>
@@ -10403,7 +10441,7 @@
         <v>18</v>
       </c>
       <c r="D101" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E101" s="17" t="s">
         <v>266</v>
@@ -10426,7 +10464,7 @@
         <v>18</v>
       </c>
       <c r="D102" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E102" s="17" t="s">
         <v>268</v>
@@ -10449,7 +10487,7 @@
         <v>18</v>
       </c>
       <c r="D103" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E103" s="17" t="s">
         <v>270</v>
@@ -10472,7 +10510,7 @@
         <v>18</v>
       </c>
       <c r="D104" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E104" s="17" t="s">
         <v>272</v>
@@ -10495,7 +10533,7 @@
         <v>18</v>
       </c>
       <c r="D105" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E105" s="17" t="s">
         <v>274</v>
@@ -10518,7 +10556,7 @@
         <v>18</v>
       </c>
       <c r="D106" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E106" s="17" t="s">
         <v>276</v>
@@ -10541,7 +10579,7 @@
         <v>18</v>
       </c>
       <c r="D107" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E107" s="17" t="s">
         <v>278</v>
@@ -10564,7 +10602,7 @@
         <v>18</v>
       </c>
       <c r="D108" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E108" s="17" t="s">
         <v>280</v>
@@ -10587,7 +10625,7 @@
         <v>18</v>
       </c>
       <c r="D109" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E109" s="17" t="s">
         <v>282</v>
@@ -10610,7 +10648,7 @@
         <v>18</v>
       </c>
       <c r="D110" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E110" s="17" t="s">
         <v>284</v>
@@ -10633,7 +10671,7 @@
         <v>18</v>
       </c>
       <c r="D111" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E111" s="17" t="s">
         <v>286</v>
@@ -10656,7 +10694,7 @@
         <v>18</v>
       </c>
       <c r="D112" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E112" s="17" t="s">
         <v>288</v>
@@ -10679,7 +10717,7 @@
         <v>18</v>
       </c>
       <c r="D113" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E113" s="17" t="s">
         <v>289</v>
@@ -10702,7 +10740,7 @@
         <v>18</v>
       </c>
       <c r="D114" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E114" s="17" t="s">
         <v>291</v>
@@ -10725,7 +10763,7 @@
         <v>18</v>
       </c>
       <c r="D115" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E115" s="17" t="s">
         <v>293</v>
@@ -10748,7 +10786,7 @@
         <v>18</v>
       </c>
       <c r="D116" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E116" s="17" t="s">
         <v>295</v>
@@ -10771,7 +10809,7 @@
         <v>18</v>
       </c>
       <c r="D117" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E117" s="17" t="s">
         <v>297</v>
@@ -10794,7 +10832,7 @@
         <v>18</v>
       </c>
       <c r="D118" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E118" s="17" t="s">
         <v>299</v>
@@ -10817,7 +10855,7 @@
         <v>18</v>
       </c>
       <c r="D119" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E119" s="24" t="s">
         <v>301</v>
@@ -10840,7 +10878,7 @@
         <v>18</v>
       </c>
       <c r="D120" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E120" s="24" t="s">
         <v>303</v>
@@ -10863,7 +10901,7 @@
         <v>18</v>
       </c>
       <c r="D121" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E121" s="24" t="s">
         <v>305</v>
@@ -10886,7 +10924,7 @@
         <v>18</v>
       </c>
       <c r="D122" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E122" s="24" t="s">
         <v>307</v>
@@ -10909,7 +10947,7 @@
         <v>18</v>
       </c>
       <c r="D123" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E123" s="24" t="s">
         <v>309</v>
@@ -10932,7 +10970,7 @@
         <v>18</v>
       </c>
       <c r="D124" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E124" s="24" t="s">
         <v>311</v>
@@ -10955,7 +10993,7 @@
         <v>18</v>
       </c>
       <c r="D125" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E125" s="24" t="s">
         <v>312</v>
@@ -10978,7 +11016,7 @@
         <v>18</v>
       </c>
       <c r="D126" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E126" s="24" t="s">
         <v>313</v>
@@ -11001,7 +11039,7 @@
         <v>18</v>
       </c>
       <c r="D127" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E127" s="24" t="s">
         <v>314</v>
@@ -11024,7 +11062,7 @@
         <v>18</v>
       </c>
       <c r="D128" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E128" s="24" t="s">
         <v>316</v>
@@ -11047,7 +11085,7 @@
         <v>18</v>
       </c>
       <c r="D129" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E129" s="24">
         <v>160183</v>
@@ -11070,7 +11108,7 @@
         <v>18</v>
       </c>
       <c r="D130" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E130" s="24" t="s">
         <v>318</v>
@@ -11093,7 +11131,7 @@
         <v>18</v>
       </c>
       <c r="D131" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E131" s="24" t="s">
         <v>320</v>
@@ -11116,7 +11154,7 @@
         <v>18</v>
       </c>
       <c r="D132" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E132" s="24" t="s">
         <v>322</v>
@@ -11139,7 +11177,7 @@
         <v>18</v>
       </c>
       <c r="D133" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E133" s="24" t="s">
         <v>324</v>
@@ -11162,7 +11200,7 @@
         <v>18</v>
       </c>
       <c r="D134" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E134" s="24">
         <v>160188</v>
@@ -11185,7 +11223,7 @@
         <v>18</v>
       </c>
       <c r="D135" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E135" s="24" t="s">
         <v>326</v>
@@ -11208,7 +11246,7 @@
         <v>18</v>
       </c>
       <c r="D136" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E136" s="24" t="s">
         <v>327</v>
@@ -11231,7 +11269,7 @@
         <v>18</v>
       </c>
       <c r="D137" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E137" s="24" t="s">
         <v>329</v>
@@ -11254,7 +11292,7 @@
         <v>18</v>
       </c>
       <c r="D138" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E138" s="24" t="s">
         <v>330</v>
@@ -11277,7 +11315,7 @@
         <v>18</v>
       </c>
       <c r="D139" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E139" s="24" t="s">
         <v>332</v>
@@ -11300,7 +11338,7 @@
         <v>18</v>
       </c>
       <c r="D140" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E140" s="24" t="s">
         <v>334</v>
@@ -11323,7 +11361,7 @@
         <v>18</v>
       </c>
       <c r="D141" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E141" s="24" t="s">
         <v>336</v>
@@ -11346,7 +11384,7 @@
         <v>18</v>
       </c>
       <c r="D142" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E142" s="24" t="s">
         <v>338</v>
@@ -11369,7 +11407,7 @@
         <v>18</v>
       </c>
       <c r="D143" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E143" s="24">
         <v>160247</v>
@@ -11392,7 +11430,7 @@
         <v>18</v>
       </c>
       <c r="D144" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E144" s="24">
         <v>160248</v>
@@ -11415,7 +11453,7 @@
         <v>18</v>
       </c>
       <c r="D145" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E145" s="24" t="s">
         <v>341</v>
@@ -11438,7 +11476,7 @@
         <v>18</v>
       </c>
       <c r="D146" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E146" s="24" t="s">
         <v>343</v>
@@ -11461,7 +11499,7 @@
         <v>18</v>
       </c>
       <c r="D147" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E147" s="24" t="s">
         <v>345</v>
@@ -11484,7 +11522,7 @@
         <v>18</v>
       </c>
       <c r="D148" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E148" s="24" t="s">
         <v>347</v>
@@ -11507,7 +11545,7 @@
         <v>18</v>
       </c>
       <c r="D149" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E149" s="24" t="s">
         <v>349</v>
@@ -11530,7 +11568,7 @@
         <v>18</v>
       </c>
       <c r="D150" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E150" s="24" t="s">
         <v>351</v>
@@ -11553,7 +11591,7 @@
         <v>18</v>
       </c>
       <c r="D151" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E151" s="24" t="s">
         <v>353</v>
@@ -11576,7 +11614,7 @@
         <v>18</v>
       </c>
       <c r="D152" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E152" s="24" t="s">
         <v>355</v>
@@ -11614,7 +11652,7 @@
         <v>18</v>
       </c>
       <c r="D154" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E154" s="24">
         <v>160263</v>
@@ -11637,7 +11675,7 @@
         <v>18</v>
       </c>
       <c r="D155" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E155" s="24">
         <v>160264</v>
@@ -11660,7 +11698,7 @@
         <v>18</v>
       </c>
       <c r="D156" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E156" s="24" t="s">
         <v>357</v>
@@ -11683,7 +11721,7 @@
         <v>18</v>
       </c>
       <c r="D157" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E157" s="24" t="s">
         <v>359</v>
@@ -11706,7 +11744,7 @@
         <v>18</v>
       </c>
       <c r="D158" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E158" s="24" t="s">
         <v>361</v>
@@ -11729,7 +11767,7 @@
         <v>18</v>
       </c>
       <c r="D159" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E159" s="24" t="s">
         <v>367</v>
@@ -11752,7 +11790,7 @@
         <v>18</v>
       </c>
       <c r="D160" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E160" s="24">
         <v>160280</v>
@@ -11775,7 +11813,7 @@
         <v>18</v>
       </c>
       <c r="D161" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E161" s="24" t="s">
         <v>657</v>
@@ -11798,7 +11836,7 @@
         <v>18</v>
       </c>
       <c r="D162" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E162" s="24" t="s">
         <v>658</v>
@@ -11821,7 +11859,7 @@
         <v>18</v>
       </c>
       <c r="D163" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E163" s="26">
         <v>160286</v>
@@ -11844,7 +11882,7 @@
         <v>18</v>
       </c>
       <c r="D164" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E164" s="26">
         <v>160287</v>
@@ -11867,7 +11905,7 @@
         <v>18</v>
       </c>
       <c r="D165" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E165" s="24">
         <v>160288</v>
@@ -11890,7 +11928,7 @@
         <v>18</v>
       </c>
       <c r="D166" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E166" s="24" t="s">
         <v>669</v>
@@ -11913,7 +11951,7 @@
         <v>18</v>
       </c>
       <c r="D167" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E167" s="26">
         <v>160291</v>
@@ -11936,7 +11974,7 @@
         <v>18</v>
       </c>
       <c r="D168" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E168" s="26">
         <v>160292</v>
@@ -11959,7 +11997,7 @@
         <v>18</v>
       </c>
       <c r="D169" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E169" s="26">
         <v>160293</v>
@@ -11982,7 +12020,7 @@
         <v>18</v>
       </c>
       <c r="D170" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E170" s="26">
         <v>160294</v>
@@ -12005,7 +12043,7 @@
         <v>18</v>
       </c>
       <c r="D171" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E171" s="24">
         <v>160300</v>
@@ -12028,7 +12066,7 @@
         <v>18</v>
       </c>
       <c r="D172" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E172" s="24">
         <v>160301</v>
@@ -12051,7 +12089,7 @@
         <v>18</v>
       </c>
       <c r="D173" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E173" s="24">
         <v>160302</v>
@@ -12074,7 +12112,7 @@
         <v>18</v>
       </c>
       <c r="D174" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E174" s="24">
         <v>160303</v>
@@ -12097,7 +12135,7 @@
         <v>18</v>
       </c>
       <c r="D175" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E175" s="17">
         <v>160307</v>
@@ -12120,7 +12158,7 @@
         <v>18</v>
       </c>
       <c r="D176" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E176" s="17">
         <v>160308</v>
@@ -12143,7 +12181,7 @@
         <v>18</v>
       </c>
       <c r="D177" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E177" s="17">
         <v>160309</v>
@@ -12166,7 +12204,7 @@
         <v>18</v>
       </c>
       <c r="D178" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E178" s="17">
         <v>160310</v>
@@ -12189,7 +12227,7 @@
         <v>18</v>
       </c>
       <c r="D179" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E179" s="17">
         <v>160311</v>
@@ -12212,7 +12250,7 @@
         <v>18</v>
       </c>
       <c r="D180" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E180" s="17">
         <v>160312</v>
@@ -12235,7 +12273,7 @@
         <v>18</v>
       </c>
       <c r="D181" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E181" s="17">
         <v>160313</v>
@@ -12258,7 +12296,7 @@
         <v>18</v>
       </c>
       <c r="D182" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E182" s="17">
         <v>160314</v>
@@ -12281,7 +12319,7 @@
         <v>18</v>
       </c>
       <c r="D183" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E183" s="17">
         <v>160315</v>
@@ -12304,7 +12342,7 @@
         <v>18</v>
       </c>
       <c r="D184" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="E184" s="17">
         <v>160316</v>
@@ -12327,7 +12365,7 @@
         <v>18</v>
       </c>
       <c r="D185" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="E185" s="17">
         <v>160317</v>
@@ -12350,7 +12388,7 @@
         <v>18</v>
       </c>
       <c r="D186" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E186" s="17">
         <v>160326</v>
@@ -12373,7 +12411,7 @@
         <v>18</v>
       </c>
       <c r="D187" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E187" s="17">
         <v>160327</v>
@@ -12396,7 +12434,7 @@
         <v>18</v>
       </c>
       <c r="D188" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E188" s="17">
         <v>160328</v>
@@ -12419,7 +12457,7 @@
         <v>18</v>
       </c>
       <c r="D189" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E189" s="17">
         <v>160329</v>
@@ -12442,7 +12480,7 @@
         <v>18</v>
       </c>
       <c r="D190" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E190" s="17">
         <v>160330</v>
@@ -12465,7 +12503,7 @@
         <v>18</v>
       </c>
       <c r="D191" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E191" s="17">
         <v>160336</v>
@@ -12488,14 +12526,14 @@
         <v>18</v>
       </c>
       <c r="D192" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="E192" s="17">
         <v>160331</v>
       </c>
       <c r="F192" s="37"/>
       <c r="G192" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -12509,16 +12547,16 @@
         <v>18</v>
       </c>
       <c r="D193" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="E193" s="17">
         <v>160332</v>
       </c>
       <c r="F193" s="37" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="G193" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -12532,16 +12570,16 @@
         <v>18</v>
       </c>
       <c r="D194" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="E194" s="17">
         <v>160333</v>
       </c>
       <c r="F194" s="17" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G194" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="195" spans="1:7" ht="30">
@@ -12555,16 +12593,16 @@
         <v>18</v>
       </c>
       <c r="D195" s="10" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="E195" s="24">
         <v>160334</v>
       </c>
       <c r="F195" s="37" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="G195" s="10" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="196" spans="1:7" ht="30">
@@ -12578,16 +12616,16 @@
         <v>18</v>
       </c>
       <c r="D196" s="10" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="E196" s="24">
         <v>160335</v>
       </c>
       <c r="F196" s="37" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="G196" s="10" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -12601,16 +12639,16 @@
         <v>18</v>
       </c>
       <c r="D197" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="E197" s="17">
         <v>160337</v>
       </c>
       <c r="F197" s="17" t="s">
+        <v>888</v>
+      </c>
+      <c r="G197" s="2" t="s">
         <v>889</v>
-      </c>
-      <c r="G197" s="2" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -12624,16 +12662,16 @@
         <v>18</v>
       </c>
       <c r="D198" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="E198" s="17">
         <v>160338</v>
       </c>
       <c r="F198" s="37" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -12647,7 +12685,7 @@
         <v>18</v>
       </c>
       <c r="D199" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="E199" s="17">
         <v>160322</v>
@@ -12656,7 +12694,7 @@
         <v>872</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -12670,7 +12708,7 @@
         <v>18</v>
       </c>
       <c r="D200" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E200" s="17">
         <v>160319</v>
@@ -12679,7 +12717,7 @@
         <v>695</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="201" spans="1:7" ht="30">
@@ -12693,7 +12731,7 @@
         <v>18</v>
       </c>
       <c r="D201" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E201" s="24">
         <v>160320</v>
@@ -12702,7 +12740,7 @@
         <v>859</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -12716,16 +12754,16 @@
         <v>18</v>
       </c>
       <c r="D202" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="E202" s="24">
         <v>160339</v>
       </c>
       <c r="F202" s="17" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G202" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -12739,16 +12777,16 @@
         <v>18</v>
       </c>
       <c r="D203" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="E203" s="24">
         <v>160340</v>
       </c>
       <c r="F203" s="17" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G203" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -12762,16 +12800,16 @@
         <v>18</v>
       </c>
       <c r="D204" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="E204" s="24">
         <v>160341</v>
       </c>
       <c r="F204" s="17" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G204" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -12785,16 +12823,16 @@
         <v>18</v>
       </c>
       <c r="D205" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="E205" s="24">
         <v>160342</v>
       </c>
       <c r="F205" s="17" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G205" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -12808,7 +12846,7 @@
         <v>18</v>
       </c>
       <c r="D206" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E206" s="17">
         <v>160347</v>
@@ -12817,7 +12855,7 @@
         <v>876</v>
       </c>
       <c r="G206" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -12831,7 +12869,7 @@
         <v>18</v>
       </c>
       <c r="D207" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E207" s="17">
         <v>160348</v>
@@ -12840,7 +12878,7 @@
         <v>876</v>
       </c>
       <c r="G207" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -12854,7 +12892,7 @@
         <v>18</v>
       </c>
       <c r="D208" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E208" s="17">
         <v>160349</v>
@@ -12863,7 +12901,7 @@
         <v>876</v>
       </c>
       <c r="G208" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -12877,7 +12915,7 @@
         <v>18</v>
       </c>
       <c r="D209" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E209" s="17">
         <v>160351</v>
@@ -12886,7 +12924,7 @@
         <v>876</v>
       </c>
       <c r="G209" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="210" spans="1:7" ht="30">
@@ -12900,16 +12938,16 @@
         <v>18</v>
       </c>
       <c r="D210" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E210" s="17">
         <v>160360</v>
       </c>
       <c r="F210" s="37" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -12923,16 +12961,16 @@
         <v>18</v>
       </c>
       <c r="D211" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="E211" s="17">
         <v>160361</v>
       </c>
       <c r="F211" s="17" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -12946,16 +12984,16 @@
         <v>18</v>
       </c>
       <c r="D212" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="E212" s="17">
         <v>160362</v>
       </c>
       <c r="F212" s="17" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -12969,16 +13007,16 @@
         <v>18</v>
       </c>
       <c r="D213" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="E213" s="17">
         <v>160363</v>
       </c>
       <c r="F213" s="17" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -12992,16 +13030,16 @@
         <v>18</v>
       </c>
       <c r="D214" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="E214" s="17">
         <v>160364</v>
       </c>
       <c r="F214" s="17" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -13015,16 +13053,16 @@
         <v>18</v>
       </c>
       <c r="D215" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="E215" s="17">
         <v>160364</v>
       </c>
       <c r="F215" s="17" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -13038,7 +13076,7 @@
         <v>18</v>
       </c>
       <c r="D216" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E216" s="17">
         <v>160366</v>
@@ -13047,7 +13085,7 @@
         <v>691</v>
       </c>
       <c r="G216" s="45" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -13061,7 +13099,7 @@
         <v>18</v>
       </c>
       <c r="D217" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E217" s="17">
         <v>160367</v>
@@ -13070,7 +13108,7 @@
         <v>691</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -13084,7 +13122,7 @@
         <v>18</v>
       </c>
       <c r="D218" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E218" s="17">
         <v>160368</v>
@@ -13093,7 +13131,7 @@
         <v>692</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -13107,7 +13145,7 @@
         <v>18</v>
       </c>
       <c r="D219" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E219" s="17">
         <v>160369</v>
@@ -13116,7 +13154,7 @@
         <v>776</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="220" spans="1:7" s="10" customFormat="1" ht="45">
@@ -13130,16 +13168,16 @@
         <v>18</v>
       </c>
       <c r="D220" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E220" s="24">
         <v>160370</v>
       </c>
       <c r="F220" s="33" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="G220" s="11" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -13153,7 +13191,7 @@
         <v>18</v>
       </c>
       <c r="D221" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E221" s="17">
         <v>160375</v>
@@ -13162,7 +13200,7 @@
         <v>709</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -13176,16 +13214,16 @@
         <v>18</v>
       </c>
       <c r="D222" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="E222" s="17">
         <v>160377</v>
       </c>
       <c r="F222" s="33" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -13199,7 +13237,7 @@
         <v>18</v>
       </c>
       <c r="D223" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E223" s="17">
         <v>160378</v>
@@ -13208,7 +13246,7 @@
         <v>754</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -13222,7 +13260,7 @@
         <v>18</v>
       </c>
       <c r="D224" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E224" s="17">
         <v>160379</v>
@@ -13231,7 +13269,7 @@
         <v>754</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -13245,7 +13283,7 @@
         <v>18</v>
       </c>
       <c r="D225" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E225" s="17">
         <v>160380</v>
@@ -13254,7 +13292,7 @@
         <v>754</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -13268,7 +13306,7 @@
         <v>18</v>
       </c>
       <c r="D226" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E226" s="17">
         <v>160381</v>
@@ -13277,7 +13315,7 @@
         <v>754</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -13291,16 +13329,16 @@
         <v>18</v>
       </c>
       <c r="D227" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E227" s="17">
         <v>160382</v>
       </c>
       <c r="F227" s="33" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -13314,16 +13352,16 @@
         <v>18</v>
       </c>
       <c r="D228" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E228" s="17">
         <v>160383</v>
       </c>
       <c r="F228" s="33" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -13337,7 +13375,7 @@
         <v>18</v>
       </c>
       <c r="D229" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E229" s="17">
         <v>160384</v>
@@ -13346,7 +13384,7 @@
         <v>754</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -13360,7 +13398,7 @@
         <v>18</v>
       </c>
       <c r="D230" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E230" s="17">
         <v>160388</v>
@@ -13369,7 +13407,7 @@
         <v>703</v>
       </c>
       <c r="G230" s="47" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -13383,13 +13421,13 @@
         <v>18</v>
       </c>
       <c r="D231" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="E231" s="17">
         <v>160394</v>
       </c>
       <c r="F231" s="33" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>252</v>
@@ -13406,16 +13444,16 @@
         <v>18</v>
       </c>
       <c r="D232" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E232" s="17">
         <v>160395</v>
       </c>
       <c r="F232" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -13429,16 +13467,16 @@
         <v>18</v>
       </c>
       <c r="D233" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E233" s="17">
         <v>160399</v>
       </c>
       <c r="F233" s="17" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G233" s="48" t="s">
         <v>1009</v>
-      </c>
-      <c r="G233" s="48" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="234" spans="1:7" ht="30">
@@ -13452,7 +13490,7 @@
         <v>18</v>
       </c>
       <c r="D234" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E234" s="17">
         <v>160400</v>
@@ -13461,7 +13499,7 @@
         <v>694</v>
       </c>
       <c r="G234" s="48" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -13475,7 +13513,7 @@
         <v>18</v>
       </c>
       <c r="D235" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E235" s="17">
         <v>160401</v>
@@ -13484,7 +13522,7 @@
         <v>841</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
   </sheetData>
@@ -13546,7 +13584,7 @@
         <v>18</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E2" s="25" t="s">
         <v>370</v>
@@ -13569,7 +13607,7 @@
         <v>18</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E3" s="25" t="s">
         <v>371</v>
@@ -13592,7 +13630,7 @@
         <v>18</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E4" s="25" t="s">
         <v>94</v>
@@ -13615,7 +13653,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E5" s="25" t="s">
         <v>126</v>
@@ -13638,7 +13676,7 @@
         <v>18</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E6" s="25" t="s">
         <v>150</v>
@@ -13661,7 +13699,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E7" s="25" t="s">
         <v>107</v>
@@ -13684,7 +13722,7 @@
         <v>18</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E8" s="25" t="s">
         <v>107</v>
@@ -13707,7 +13745,7 @@
         <v>18</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E9" s="25" t="s">
         <v>112</v>
@@ -13730,7 +13768,7 @@
         <v>18</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E10" s="25" t="s">
         <v>374</v>
@@ -13751,7 +13789,7 @@
         <v>18</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E11" s="25" t="s">
         <v>376</v>
@@ -13772,7 +13810,7 @@
         <v>18</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E12" s="25" t="s">
         <v>378</v>
@@ -13793,7 +13831,7 @@
         <v>18</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E13" s="25" t="s">
         <v>380</v>
@@ -13814,7 +13852,7 @@
         <v>18</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E14" s="25" t="s">
         <v>382</v>
@@ -13835,7 +13873,7 @@
         <v>18</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E15" s="25" t="s">
         <v>384</v>
@@ -13856,7 +13894,7 @@
         <v>18</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E16" s="25" t="s">
         <v>386</v>
@@ -13879,7 +13917,7 @@
         <v>18</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E17" s="24" t="s">
         <v>388</v>
@@ -13902,7 +13940,7 @@
         <v>18</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E18" s="24" t="s">
         <v>390</v>
@@ -13925,7 +13963,7 @@
         <v>18</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E19" s="24" t="s">
         <v>392</v>
@@ -13948,7 +13986,7 @@
         <v>18</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E20" s="24" t="s">
         <v>394</v>
@@ -13971,7 +14009,7 @@
         <v>18</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E21" s="24" t="s">
         <v>396</v>
@@ -13994,7 +14032,7 @@
         <v>18</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E22" s="24" t="s">
         <v>398</v>
@@ -14017,7 +14055,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E23" s="24" t="s">
         <v>400</v>
@@ -14040,7 +14078,7 @@
         <v>18</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E24" s="24" t="s">
         <v>402</v>
@@ -14063,7 +14101,7 @@
         <v>18</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E25" s="24" t="s">
         <v>404</v>
@@ -14086,7 +14124,7 @@
         <v>18</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E26" s="24" t="s">
         <v>405</v>
@@ -14109,7 +14147,7 @@
         <v>18</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E27" s="24" t="s">
         <v>406</v>
@@ -14132,7 +14170,7 @@
         <v>18</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E28" s="24" t="s">
         <v>407</v>
@@ -14155,7 +14193,7 @@
         <v>18</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E29" s="24" t="s">
         <v>409</v>
@@ -14178,7 +14216,7 @@
         <v>18</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E30" s="24" t="s">
         <v>411</v>
@@ -14201,7 +14239,7 @@
         <v>18</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E31" s="24" t="s">
         <v>413</v>
@@ -14224,7 +14262,7 @@
         <v>18</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E32" s="24" t="s">
         <v>355</v>
@@ -14247,7 +14285,7 @@
         <v>18</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E33" s="24" t="s">
         <v>152</v>
@@ -14270,7 +14308,7 @@
         <v>18</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E34" s="24" t="s">
         <v>154</v>
@@ -14293,7 +14331,7 @@
         <v>18</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E35" s="24" t="s">
         <v>156</v>
@@ -14316,7 +14354,7 @@
         <v>18</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E36" s="24" t="s">
         <v>157</v>
@@ -14339,7 +14377,7 @@
         <v>18</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E37" s="17" t="s">
         <v>158</v>
@@ -14362,7 +14400,7 @@
         <v>18</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E38" s="17" t="s">
         <v>160</v>
@@ -14385,7 +14423,7 @@
         <v>18</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E39" s="17" t="s">
         <v>162</v>
@@ -14408,7 +14446,7 @@
         <v>18</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E40" s="17" t="s">
         <v>164</v>
@@ -14431,7 +14469,7 @@
         <v>18</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E41" s="17" t="s">
         <v>166</v>
@@ -14454,7 +14492,7 @@
         <v>18</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E42" s="17" t="s">
         <v>168</v>
@@ -14477,7 +14515,7 @@
         <v>18</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E43" s="17" t="s">
         <v>170</v>
@@ -14500,7 +14538,7 @@
         <v>18</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E44" s="17" t="s">
         <v>172</v>
@@ -14523,7 +14561,7 @@
         <v>18</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E45" s="17" t="s">
         <v>174</v>
@@ -14546,7 +14584,7 @@
         <v>18</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E46" s="17" t="s">
         <v>176</v>
@@ -14569,7 +14607,7 @@
         <v>18</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E47" s="17" t="s">
         <v>178</v>
@@ -14592,7 +14630,7 @@
         <v>18</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E48" s="17" t="s">
         <v>180</v>
@@ -14615,7 +14653,7 @@
         <v>18</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E49" s="17" t="s">
         <v>182</v>
@@ -14638,7 +14676,7 @@
         <v>18</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E50" s="17" t="s">
         <v>184</v>
@@ -14661,7 +14699,7 @@
         <v>18</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E51" s="17" t="s">
         <v>186</v>
@@ -14684,7 +14722,7 @@
         <v>18</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E52" s="17" t="s">
         <v>187</v>
@@ -14707,7 +14745,7 @@
         <v>18</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E53" s="17" t="s">
         <v>189</v>
@@ -14730,7 +14768,7 @@
         <v>18</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E54" s="17" t="s">
         <v>191</v>
@@ -14753,7 +14791,7 @@
         <v>18</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E55" s="17" t="s">
         <v>192</v>
@@ -14776,7 +14814,7 @@
         <v>18</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E56" s="17" t="s">
         <v>193</v>
@@ -14799,7 +14837,7 @@
         <v>18</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E57" s="17" t="s">
         <v>194</v>
@@ -14822,7 +14860,7 @@
         <v>18</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E58" s="17" t="s">
         <v>196</v>
@@ -14845,7 +14883,7 @@
         <v>18</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E59" s="17" t="s">
         <v>197</v>
@@ -14868,7 +14906,7 @@
         <v>18</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E60" s="17" t="s">
         <v>199</v>
@@ -14891,7 +14929,7 @@
         <v>18</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E61" s="17" t="s">
         <v>201</v>
@@ -14914,7 +14952,7 @@
         <v>18</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E62" s="17" t="s">
         <v>202</v>
@@ -14937,7 +14975,7 @@
         <v>18</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E63" s="17" t="s">
         <v>204</v>
@@ -14960,7 +14998,7 @@
         <v>18</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E64" s="17" t="s">
         <v>206</v>
@@ -14983,7 +15021,7 @@
         <v>18</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E65" s="17" t="s">
         <v>208</v>
@@ -15006,7 +15044,7 @@
         <v>18</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E66" s="17" t="s">
         <v>210</v>
@@ -15029,7 +15067,7 @@
         <v>18</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E67" s="17" t="s">
         <v>212</v>
@@ -15052,7 +15090,7 @@
         <v>18</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E68" s="17" t="s">
         <v>214</v>
@@ -15075,7 +15113,7 @@
         <v>18</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E69" s="17" t="s">
         <v>216</v>
@@ -15098,7 +15136,7 @@
         <v>18</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E70" s="17" t="s">
         <v>218</v>
@@ -15121,7 +15159,7 @@
         <v>18</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E71" s="17" t="s">
         <v>220</v>
@@ -15144,7 +15182,7 @@
         <v>18</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E72" s="17" t="s">
         <v>222</v>
@@ -15167,7 +15205,7 @@
         <v>18</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E73" s="17" t="s">
         <v>224</v>
@@ -15190,7 +15228,7 @@
         <v>18</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E74" s="17" t="s">
         <v>226</v>
@@ -15213,7 +15251,7 @@
         <v>18</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E75" s="17" t="s">
         <v>228</v>
@@ -15236,7 +15274,7 @@
         <v>18</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E76" s="17" t="s">
         <v>230</v>
@@ -15259,7 +15297,7 @@
         <v>18</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E77" s="17" t="s">
         <v>232</v>
@@ -15282,7 +15320,7 @@
         <v>18</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E78" s="17" t="s">
         <v>234</v>
@@ -15305,7 +15343,7 @@
         <v>18</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E79" s="17" t="s">
         <v>236</v>
@@ -15328,7 +15366,7 @@
         <v>18</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E80" s="17" t="s">
         <v>238</v>
@@ -15351,7 +15389,7 @@
         <v>18</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E81" s="17" t="s">
         <v>240</v>
@@ -15374,7 +15412,7 @@
         <v>18</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E82" s="17" t="s">
         <v>242</v>
@@ -15397,7 +15435,7 @@
         <v>18</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E83" s="17" t="s">
         <v>244</v>
@@ -15420,7 +15458,7 @@
         <v>18</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E84" s="17" t="s">
         <v>246</v>
@@ -15443,7 +15481,7 @@
         <v>18</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E85" s="17" t="s">
         <v>247</v>
@@ -15466,7 +15504,7 @@
         <v>18</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E86" s="17" t="s">
         <v>249</v>
@@ -15489,7 +15527,7 @@
         <v>18</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E87" s="17" t="s">
         <v>251</v>
@@ -15512,7 +15550,7 @@
         <v>18</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E88" s="17" t="s">
         <v>253</v>
@@ -15535,7 +15573,7 @@
         <v>18</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E89" s="17" t="s">
         <v>254</v>
@@ -15558,7 +15596,7 @@
         <v>18</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E90" s="17" t="s">
         <v>255</v>
@@ -15581,7 +15619,7 @@
         <v>18</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E91" s="17" t="s">
         <v>256</v>
@@ -15604,7 +15642,7 @@
         <v>18</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E92" s="17" t="s">
         <v>258</v>
@@ -15627,7 +15665,7 @@
         <v>18</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E93" s="17" t="s">
         <v>260</v>
@@ -15650,7 +15688,7 @@
         <v>18</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E94" s="17" t="s">
         <v>262</v>
@@ -15673,7 +15711,7 @@
         <v>18</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E95" s="17" t="s">
         <v>264</v>
@@ -15696,7 +15734,7 @@
         <v>18</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E96" s="17" t="s">
         <v>266</v>
@@ -15719,7 +15757,7 @@
         <v>18</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E97" s="17" t="s">
         <v>268</v>
@@ -15742,7 +15780,7 @@
         <v>18</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E98" s="17" t="s">
         <v>270</v>
@@ -15765,7 +15803,7 @@
         <v>18</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E99" s="17" t="s">
         <v>272</v>
@@ -15788,7 +15826,7 @@
         <v>18</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E100" s="17" t="s">
         <v>274</v>
@@ -15811,7 +15849,7 @@
         <v>18</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E101" s="17" t="s">
         <v>276</v>
@@ -15834,7 +15872,7 @@
         <v>18</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E102" s="17" t="s">
         <v>278</v>
@@ -15857,7 +15895,7 @@
         <v>18</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E103" s="17" t="s">
         <v>280</v>
@@ -15880,7 +15918,7 @@
         <v>18</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E104" s="17" t="s">
         <v>282</v>
@@ -15903,7 +15941,7 @@
         <v>18</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E105" s="17" t="s">
         <v>284</v>
@@ -15926,7 +15964,7 @@
         <v>18</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E106" s="17" t="s">
         <v>286</v>
@@ -15949,7 +15987,7 @@
         <v>18</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E107" s="17" t="s">
         <v>288</v>
@@ -15972,7 +16010,7 @@
         <v>18</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E108" s="17" t="s">
         <v>289</v>
@@ -15995,7 +16033,7 @@
         <v>18</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E109" s="17" t="s">
         <v>291</v>
@@ -16018,7 +16056,7 @@
         <v>18</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E110" s="17" t="s">
         <v>293</v>
@@ -16041,7 +16079,7 @@
         <v>18</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E111" s="17" t="s">
         <v>295</v>
@@ -16064,7 +16102,7 @@
         <v>18</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E112" s="17" t="s">
         <v>297</v>
@@ -16087,7 +16125,7 @@
         <v>18</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E113" s="17" t="s">
         <v>299</v>
@@ -16110,7 +16148,7 @@
         <v>18</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E114" s="24" t="s">
         <v>301</v>
@@ -16133,7 +16171,7 @@
         <v>18</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E115" s="24" t="s">
         <v>303</v>
@@ -16156,7 +16194,7 @@
         <v>18</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E116" s="24" t="s">
         <v>305</v>
@@ -16179,7 +16217,7 @@
         <v>18</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E117" s="24" t="s">
         <v>307</v>
@@ -16202,7 +16240,7 @@
         <v>18</v>
       </c>
       <c r="D118" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E118" s="24" t="s">
         <v>309</v>
@@ -16225,7 +16263,7 @@
         <v>18</v>
       </c>
       <c r="D119" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E119" s="24" t="s">
         <v>311</v>
@@ -16248,7 +16286,7 @@
         <v>18</v>
       </c>
       <c r="D120" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E120" s="24" t="s">
         <v>312</v>
@@ -16271,7 +16309,7 @@
         <v>18</v>
       </c>
       <c r="D121" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E121" s="24" t="s">
         <v>313</v>
@@ -16294,7 +16332,7 @@
         <v>18</v>
       </c>
       <c r="D122" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E122" s="24" t="s">
         <v>314</v>
@@ -16317,7 +16355,7 @@
         <v>18</v>
       </c>
       <c r="D123" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E123" s="24" t="s">
         <v>316</v>
@@ -16382,7 +16420,7 @@
         <v>18</v>
       </c>
       <c r="D127" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E127" s="24">
         <v>160183</v>
@@ -16405,7 +16443,7 @@
         <v>18</v>
       </c>
       <c r="D128" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E128" s="24" t="s">
         <v>318</v>
@@ -16428,7 +16466,7 @@
         <v>18</v>
       </c>
       <c r="D129" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E129" s="24" t="s">
         <v>320</v>
@@ -16451,7 +16489,7 @@
         <v>18</v>
       </c>
       <c r="D130" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E130" s="24" t="s">
         <v>322</v>
@@ -16474,7 +16512,7 @@
         <v>18</v>
       </c>
       <c r="D131" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E131" s="24" t="s">
         <v>324</v>
@@ -16497,7 +16535,7 @@
         <v>18</v>
       </c>
       <c r="D132" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E132" s="24" t="s">
         <v>398</v>
@@ -16520,7 +16558,7 @@
         <v>18</v>
       </c>
       <c r="D133" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E133" s="24" t="s">
         <v>400</v>
@@ -16543,7 +16581,7 @@
         <v>18</v>
       </c>
       <c r="D134" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E134" s="24" t="s">
         <v>402</v>
@@ -16566,7 +16604,7 @@
         <v>18</v>
       </c>
       <c r="D135" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E135" s="24" t="s">
         <v>404</v>
@@ -16589,7 +16627,7 @@
         <v>18</v>
       </c>
       <c r="D136" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E136" s="24" t="s">
         <v>405</v>
@@ -16612,7 +16650,7 @@
         <v>18</v>
       </c>
       <c r="D137" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E137" s="24" t="s">
         <v>406</v>
@@ -16635,7 +16673,7 @@
         <v>18</v>
       </c>
       <c r="D138" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E138" s="24" t="s">
         <v>407</v>
@@ -16658,7 +16696,7 @@
         <v>18</v>
       </c>
       <c r="D139" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E139" s="24" t="s">
         <v>675</v>
@@ -16681,7 +16719,7 @@
         <v>18</v>
       </c>
       <c r="D140" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E140" s="24" t="s">
         <v>409</v>
@@ -16704,7 +16742,7 @@
         <v>18</v>
       </c>
       <c r="D141" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E141" s="24" t="s">
         <v>326</v>
@@ -16727,7 +16765,7 @@
         <v>18</v>
       </c>
       <c r="D142" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E142" s="24" t="s">
         <v>327</v>
@@ -16750,7 +16788,7 @@
         <v>18</v>
       </c>
       <c r="D143" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E143" s="24" t="s">
         <v>329</v>
@@ -16773,7 +16811,7 @@
         <v>18</v>
       </c>
       <c r="D144" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E144" s="24" t="s">
         <v>330</v>
@@ -16796,7 +16834,7 @@
         <v>18</v>
       </c>
       <c r="D145" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E145" s="24" t="s">
         <v>332</v>
@@ -16819,7 +16857,7 @@
         <v>18</v>
       </c>
       <c r="D146" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E146" s="24" t="s">
         <v>334</v>
@@ -16842,7 +16880,7 @@
         <v>18</v>
       </c>
       <c r="D147" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E147" s="24" t="s">
         <v>336</v>
@@ -16865,7 +16903,7 @@
         <v>18</v>
       </c>
       <c r="D148" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E148" s="24" t="s">
         <v>338</v>
@@ -16888,7 +16926,7 @@
         <v>18</v>
       </c>
       <c r="D149" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E149" s="24">
         <v>160247</v>
@@ -16911,7 +16949,7 @@
         <v>18</v>
       </c>
       <c r="D150" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E150" s="24">
         <v>160248</v>
@@ -16934,7 +16972,7 @@
         <v>18</v>
       </c>
       <c r="D151" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E151" s="24" t="s">
         <v>341</v>
@@ -16957,7 +16995,7 @@
         <v>18</v>
       </c>
       <c r="D152" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E152" s="24" t="s">
         <v>343</v>
@@ -16980,7 +17018,7 @@
         <v>18</v>
       </c>
       <c r="D153" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E153" s="24" t="s">
         <v>345</v>
@@ -17003,7 +17041,7 @@
         <v>18</v>
       </c>
       <c r="D154" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E154" s="24" t="s">
         <v>347</v>
@@ -17026,7 +17064,7 @@
         <v>18</v>
       </c>
       <c r="D155" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E155" s="24" t="s">
         <v>349</v>
@@ -17049,7 +17087,7 @@
         <v>18</v>
       </c>
       <c r="D156" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E156" s="24" t="s">
         <v>351</v>
@@ -17072,7 +17110,7 @@
         <v>18</v>
       </c>
       <c r="D157" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E157" s="24" t="s">
         <v>353</v>
@@ -17095,7 +17133,7 @@
         <v>18</v>
       </c>
       <c r="D158" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E158" s="24" t="s">
         <v>355</v>
@@ -17118,7 +17156,7 @@
         <v>18</v>
       </c>
       <c r="D159" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E159" s="24">
         <v>160264</v>
@@ -17141,7 +17179,7 @@
         <v>18</v>
       </c>
       <c r="D160" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E160" s="17" t="s">
         <v>357</v>
@@ -17164,7 +17202,7 @@
         <v>18</v>
       </c>
       <c r="D161" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E161" s="17" t="s">
         <v>359</v>
@@ -17187,7 +17225,7 @@
         <v>18</v>
       </c>
       <c r="D162" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E162" s="24" t="s">
         <v>361</v>
@@ -17210,7 +17248,7 @@
         <v>18</v>
       </c>
       <c r="D163" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E163" s="24" t="s">
         <v>786</v>
@@ -17233,7 +17271,7 @@
         <v>18</v>
       </c>
       <c r="D164" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E164" s="24" t="s">
         <v>787</v>
@@ -17256,7 +17294,7 @@
         <v>18</v>
       </c>
       <c r="D165" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E165" s="24" t="s">
         <v>788</v>
@@ -17279,7 +17317,7 @@
         <v>18</v>
       </c>
       <c r="D166" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E166" s="24" t="s">
         <v>789</v>
@@ -17302,7 +17340,7 @@
         <v>18</v>
       </c>
       <c r="D167" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E167" s="24">
         <v>160280</v>
@@ -17325,7 +17363,7 @@
         <v>18</v>
       </c>
       <c r="D168" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E168" s="24">
         <v>160281</v>
@@ -17348,7 +17386,7 @@
         <v>18</v>
       </c>
       <c r="D169" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E169" s="24">
         <v>160282</v>
@@ -17371,7 +17409,7 @@
         <v>18</v>
       </c>
       <c r="D170" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E170" s="26">
         <v>160284</v>
@@ -17394,7 +17432,7 @@
         <v>18</v>
       </c>
       <c r="D171" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E171" s="26">
         <v>160285</v>
@@ -17417,7 +17455,7 @@
         <v>18</v>
       </c>
       <c r="D172" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E172" s="26">
         <v>160286</v>
@@ -17440,7 +17478,7 @@
         <v>18</v>
       </c>
       <c r="D173" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E173" s="26">
         <v>160287</v>
@@ -17463,7 +17501,7 @@
         <v>18</v>
       </c>
       <c r="D174" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E174" s="17">
         <v>160288</v>
@@ -17486,7 +17524,7 @@
         <v>18</v>
       </c>
       <c r="D175" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E175" s="24" t="s">
         <v>669</v>
@@ -17507,7 +17545,7 @@
         <v>18</v>
       </c>
       <c r="D176" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E176" s="26">
         <v>160294</v>
@@ -17530,7 +17568,7 @@
         <v>18</v>
       </c>
       <c r="D177" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E177" s="24">
         <v>160300</v>
@@ -17553,7 +17591,7 @@
         <v>18</v>
       </c>
       <c r="D178" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E178" s="24">
         <v>160301</v>
@@ -17576,7 +17614,7 @@
         <v>18</v>
       </c>
       <c r="D179" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E179" s="24">
         <v>160303</v>
@@ -17599,7 +17637,7 @@
         <v>18</v>
       </c>
       <c r="D180" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E180" s="24">
         <v>160304</v>
@@ -17622,7 +17660,7 @@
         <v>18</v>
       </c>
       <c r="D181" s="21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E181" s="24">
         <v>160320</v>
@@ -17631,7 +17669,7 @@
         <v>859</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -17645,7 +17683,7 @@
         <v>18</v>
       </c>
       <c r="D182" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E182" s="17">
         <v>160346</v>
@@ -17654,7 +17692,7 @@
         <v>691</v>
       </c>
       <c r="G182" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -17668,7 +17706,7 @@
         <v>18</v>
       </c>
       <c r="D183" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E183" s="17">
         <v>160347</v>
@@ -17677,7 +17715,7 @@
         <v>876</v>
       </c>
       <c r="G183" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -17691,7 +17729,7 @@
         <v>18</v>
       </c>
       <c r="D184" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E184" s="17">
         <v>160348</v>
@@ -17700,7 +17738,7 @@
         <v>876</v>
       </c>
       <c r="G184" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -17714,7 +17752,7 @@
         <v>18</v>
       </c>
       <c r="D185" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E185" s="17">
         <v>160349</v>
@@ -17723,7 +17761,7 @@
         <v>876</v>
       </c>
       <c r="G185" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -17737,7 +17775,7 @@
         <v>18</v>
       </c>
       <c r="D186" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E186" s="17">
         <v>160351</v>
@@ -17746,7 +17784,7 @@
         <v>876</v>
       </c>
       <c r="G186" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -17760,7 +17798,7 @@
         <v>18</v>
       </c>
       <c r="D187" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E187" s="17">
         <v>160366</v>
@@ -17769,7 +17807,7 @@
         <v>691</v>
       </c>
       <c r="G187" s="45" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -17783,7 +17821,7 @@
         <v>18</v>
       </c>
       <c r="D188" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E188" s="17">
         <v>160367</v>
@@ -17792,7 +17830,7 @@
         <v>691</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="189" spans="1:7" s="10" customFormat="1" ht="30">
@@ -17806,7 +17844,7 @@
         <v>18</v>
       </c>
       <c r="D189" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E189" s="24">
         <v>160368</v>
@@ -17815,7 +17853,7 @@
         <v>692</v>
       </c>
       <c r="G189" s="11" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="190" spans="1:7" s="10" customFormat="1" ht="45">
@@ -17829,16 +17867,16 @@
         <v>18</v>
       </c>
       <c r="D190" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E190" s="24">
         <v>160370</v>
       </c>
       <c r="F190" s="33" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="G190" s="11" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -17852,16 +17890,16 @@
         <v>18</v>
       </c>
       <c r="D191" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E191" s="17">
         <v>160395</v>
       </c>
       <c r="F191" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="192" spans="1:7" ht="30">
@@ -17875,7 +17913,7 @@
         <v>18</v>
       </c>
       <c r="D192" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E192" s="17">
         <v>160400</v>
@@ -17884,7 +17922,7 @@
         <v>694</v>
       </c>
       <c r="G192" s="48" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -17898,7 +17936,7 @@
         <v>18</v>
       </c>
       <c r="D193" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E193" s="17">
         <v>160401</v>
@@ -17907,7 +17945,7 @@
         <v>841</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
   </sheetData>
@@ -17968,7 +18006,7 @@
         <v>18</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E2" s="29" t="s">
         <v>416</v>
@@ -17989,7 +18027,7 @@
         <v>18</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E3" s="29" t="s">
         <v>89</v>
@@ -18012,7 +18050,7 @@
         <v>18</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E4" s="29" t="s">
         <v>418</v>
@@ -18035,7 +18073,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E5" s="29" t="s">
         <v>420</v>
@@ -18058,7 +18096,7 @@
         <v>18</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E6" s="29" t="s">
         <v>424</v>
@@ -18081,7 +18119,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E7" s="29" t="s">
         <v>424</v>
@@ -18104,7 +18142,7 @@
         <v>18</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E8" s="29" t="s">
         <v>427</v>
@@ -18127,7 +18165,7 @@
         <v>18</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E9" s="29" t="s">
         <v>427</v>
@@ -18150,7 +18188,7 @@
         <v>18</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E10" s="29" t="s">
         <v>422</v>
@@ -18171,7 +18209,7 @@
         <v>18</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E11" s="29" t="s">
         <v>130</v>
@@ -18194,7 +18232,7 @@
         <v>18</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E12" s="24" t="s">
         <v>440</v>
@@ -18215,7 +18253,7 @@
         <v>18</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E13" s="24" t="s">
         <v>442</v>
@@ -18236,7 +18274,7 @@
         <v>18</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E14" s="24" t="s">
         <v>444</v>
@@ -18257,7 +18295,7 @@
         <v>18</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E15" s="24" t="s">
         <v>446</v>
@@ -18278,7 +18316,7 @@
         <v>18</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E16" s="24" t="s">
         <v>448</v>
@@ -18299,7 +18337,7 @@
         <v>18</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E17" s="24" t="s">
         <v>450</v>
@@ -18322,7 +18360,7 @@
         <v>18</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E18" s="24" t="s">
         <v>452</v>
@@ -18345,7 +18383,7 @@
         <v>18</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E19" s="24" t="s">
         <v>454</v>
@@ -18368,7 +18406,7 @@
         <v>18</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E20" s="24" t="s">
         <v>456</v>
@@ -18391,7 +18429,7 @@
         <v>18</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E21" s="24" t="s">
         <v>458</v>
@@ -18414,7 +18452,7 @@
         <v>18</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E22" s="24" t="s">
         <v>459</v>
@@ -18437,7 +18475,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E23" s="24" t="s">
         <v>461</v>
@@ -18458,7 +18496,7 @@
         <v>18</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E24" s="24" t="s">
         <v>463</v>
@@ -18479,7 +18517,7 @@
         <v>18</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E25" s="24" t="s">
         <v>465</v>
@@ -18500,7 +18538,7 @@
         <v>18</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E26" s="24" t="s">
         <v>466</v>
@@ -18523,7 +18561,7 @@
         <v>18</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="E27" s="24" t="s">
         <v>669</v>
@@ -18546,7 +18584,7 @@
         <v>18</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="E28" s="24" t="s">
         <v>468</v>
@@ -18569,7 +18607,7 @@
         <v>18</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="E29" s="24" t="s">
         <v>469</v>
@@ -18592,7 +18630,7 @@
         <v>18</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="E30" s="33" t="s">
         <v>430</v>
@@ -18615,7 +18653,7 @@
         <v>18</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="E31" s="33" t="s">
         <v>431</v>
@@ -18638,7 +18676,7 @@
         <v>18</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="E32" s="33" t="s">
         <v>433</v>
@@ -18661,7 +18699,7 @@
         <v>18</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="E33" s="24" t="s">
         <v>434</v>
@@ -18684,7 +18722,7 @@
         <v>18</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="E34" s="24" t="s">
         <v>436</v>
@@ -18707,7 +18745,7 @@
         <v>18</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="E35" s="24" t="s">
         <v>437</v>
@@ -18730,7 +18768,7 @@
         <v>18</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="E36" s="24" t="s">
         <v>439</v>
@@ -18753,7 +18791,7 @@
         <v>18</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="E37" s="24">
         <v>160289</v>
@@ -18776,7 +18814,7 @@
         <v>18</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="E38" s="24">
         <v>160290</v>
@@ -18799,7 +18837,7 @@
         <v>18</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="E39" s="24">
         <v>160306</v>
@@ -18823,7 +18861,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -18869,7 +18907,7 @@
         <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E2" s="28" t="s">
         <v>476</v>
@@ -18892,7 +18930,7 @@
         <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E3" s="28" t="s">
         <v>478</v>
@@ -18915,7 +18953,7 @@
         <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E4" s="28" t="s">
         <v>480</v>
@@ -18936,7 +18974,7 @@
         <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E5" s="28" t="s">
         <v>124</v>
@@ -18959,7 +18997,7 @@
         <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E6" s="28" t="s">
         <v>448</v>
@@ -18980,7 +19018,7 @@
         <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E7" s="28" t="s">
         <v>483</v>
@@ -19003,7 +19041,7 @@
         <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E8" s="28" t="s">
         <v>485</v>
@@ -19026,7 +19064,7 @@
         <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E9" s="28" t="s">
         <v>487</v>
@@ -19047,7 +19085,7 @@
         <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E10" s="24" t="s">
         <v>489</v>
@@ -19070,7 +19108,7 @@
         <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E11" s="24" t="s">
         <v>491</v>
@@ -19093,7 +19131,7 @@
         <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E12" s="24" t="s">
         <v>493</v>
@@ -19116,7 +19154,7 @@
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E13" s="24" t="s">
         <v>494</v>
@@ -19139,7 +19177,7 @@
         <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E14" s="24" t="s">
         <v>495</v>
@@ -19162,7 +19200,7 @@
         <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E15" s="24" t="s">
         <v>497</v>
@@ -19185,7 +19223,7 @@
         <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E16" s="24" t="s">
         <v>499</v>
@@ -19208,7 +19246,7 @@
         <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E17" s="24" t="s">
         <v>501</v>
@@ -19231,7 +19269,7 @@
         <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E18" s="24" t="s">
         <v>502</v>
@@ -19254,7 +19292,7 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E19" s="24" t="s">
         <v>504</v>
@@ -19277,7 +19315,7 @@
         <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E20" s="24" t="s">
         <v>506</v>
@@ -19300,7 +19338,7 @@
         <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E21" s="24" t="s">
         <v>508</v>
@@ -19323,7 +19361,7 @@
         <v>18</v>
       </c>
       <c r="D22" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E22" s="24" t="s">
         <v>510</v>
@@ -19346,7 +19384,7 @@
         <v>18</v>
       </c>
       <c r="D23" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E23" s="24" t="s">
         <v>512</v>
@@ -19369,7 +19407,7 @@
         <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E24" s="24" t="s">
         <v>513</v>
@@ -19392,7 +19430,7 @@
         <v>18</v>
       </c>
       <c r="D25" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E25" s="24" t="s">
         <v>355</v>
@@ -19415,7 +19453,7 @@
         <v>18</v>
       </c>
       <c r="D26" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E26" s="17" t="s">
         <v>515</v>
@@ -19438,7 +19476,7 @@
         <v>18</v>
       </c>
       <c r="D27" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E27" s="17" t="s">
         <v>517</v>
@@ -19461,7 +19499,7 @@
         <v>18</v>
       </c>
       <c r="D28" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E28" s="17" t="s">
         <v>519</v>
@@ -19484,7 +19522,7 @@
         <v>18</v>
       </c>
       <c r="D29" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E29" s="17" t="s">
         <v>661</v>
@@ -19507,7 +19545,7 @@
         <v>18</v>
       </c>
       <c r="D30" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E30" s="26">
         <v>160284</v>
@@ -19530,7 +19568,7 @@
         <v>18</v>
       </c>
       <c r="D31" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E31" s="26">
         <v>160285</v>
@@ -19553,7 +19591,7 @@
         <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E32" s="26">
         <v>160286</v>
@@ -19576,7 +19614,7 @@
         <v>18</v>
       </c>
       <c r="D33" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E33" s="26">
         <v>160287</v>
@@ -19599,7 +19637,7 @@
         <v>18</v>
       </c>
       <c r="D34" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E34" s="17">
         <v>160288</v>
@@ -19622,7 +19660,7 @@
         <v>18</v>
       </c>
       <c r="D35" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E35" s="24" t="s">
         <v>669</v>
@@ -19643,7 +19681,7 @@
         <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E36" s="26">
         <v>160305</v>
@@ -19666,16 +19704,16 @@
         <v>18</v>
       </c>
       <c r="D37" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E37" s="17">
         <v>160395</v>
       </c>
       <c r="F37" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="30">
@@ -19689,7 +19727,7 @@
         <v>18</v>
       </c>
       <c r="D38" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E38" s="26">
         <v>160400</v>
@@ -19698,7 +19736,7 @@
         <v>694</v>
       </c>
       <c r="G38" s="48" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -19712,7 +19750,7 @@
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E39" s="26">
         <v>160401</v>
@@ -19721,7 +19759,99 @@
         <v>841</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>1012</v>
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="60">
+      <c r="A40" t="s">
+        <v>475</v>
+      </c>
+      <c r="B40">
+        <v>400</v>
+      </c>
+      <c r="C40" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" t="s">
+        <v>969</v>
+      </c>
+      <c r="E40" s="26">
+        <v>160404</v>
+      </c>
+      <c r="F40" s="24" t="s">
+        <v>695</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="30">
+      <c r="A41" t="s">
+        <v>475</v>
+      </c>
+      <c r="B41">
+        <v>400</v>
+      </c>
+      <c r="C41" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" t="s">
+        <v>969</v>
+      </c>
+      <c r="E41" s="26">
+        <v>160405</v>
+      </c>
+      <c r="F41" s="24" t="s">
+        <v>695</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="45">
+      <c r="A42" t="s">
+        <v>475</v>
+      </c>
+      <c r="B42">
+        <v>400</v>
+      </c>
+      <c r="C42" t="s">
+        <v>18</v>
+      </c>
+      <c r="D42" t="s">
+        <v>969</v>
+      </c>
+      <c r="E42" s="26">
+        <v>160406</v>
+      </c>
+      <c r="F42" s="24" t="s">
+        <v>695</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="45">
+      <c r="A43" t="s">
+        <v>475</v>
+      </c>
+      <c r="B43">
+        <v>400</v>
+      </c>
+      <c r="C43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D43" t="s">
+        <v>969</v>
+      </c>
+      <c r="E43" s="26">
+        <v>160407</v>
+      </c>
+      <c r="F43" s="24" t="s">
+        <v>695</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>1016</v>
       </c>
     </row>
   </sheetData>
@@ -19781,7 +19911,7 @@
         <v>18</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E2" s="29" t="s">
         <v>89</v>
@@ -19804,7 +19934,7 @@
         <v>18</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E3" s="29" t="s">
         <v>418</v>
@@ -19827,7 +19957,7 @@
         <v>18</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E4" s="29" t="s">
         <v>420</v>
@@ -19850,7 +19980,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E5" s="29" t="s">
         <v>424</v>
@@ -19873,7 +20003,7 @@
         <v>18</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E6" s="29" t="s">
         <v>424</v>
@@ -19896,7 +20026,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E7" s="29" t="s">
         <v>427</v>
@@ -19919,7 +20049,7 @@
         <v>18</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E8" s="29" t="s">
         <v>427</v>
@@ -19942,7 +20072,7 @@
         <v>18</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E9" s="29" t="s">
         <v>422</v>
@@ -19963,7 +20093,7 @@
         <v>18</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E10" s="29" t="s">
         <v>130</v>
@@ -19986,7 +20116,7 @@
         <v>18</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E11" s="29" t="s">
         <v>440</v>
@@ -20007,7 +20137,7 @@
         <v>18</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E12" s="29" t="s">
         <v>442</v>
@@ -20028,7 +20158,7 @@
         <v>18</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E13" s="29" t="s">
         <v>444</v>
@@ -20049,7 +20179,7 @@
         <v>18</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E14" s="29" t="s">
         <v>446</v>
@@ -20070,7 +20200,7 @@
         <v>18</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E15" s="29" t="s">
         <v>448</v>
@@ -20091,7 +20221,7 @@
         <v>18</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E16" s="24" t="s">
         <v>461</v>
@@ -20112,7 +20242,7 @@
         <v>18</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E17" s="24" t="s">
         <v>463</v>
@@ -20133,7 +20263,7 @@
         <v>18</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E18" s="24" t="s">
         <v>465</v>
@@ -20154,7 +20284,7 @@
         <v>18</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E19" s="24" t="s">
         <v>466</v>
@@ -20177,7 +20307,7 @@
         <v>18</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="E20" s="24" t="s">
         <v>669</v>
@@ -20200,7 +20330,7 @@
         <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="E21" s="33" t="s">
         <v>430</v>
@@ -20223,7 +20353,7 @@
         <v>18</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="E22" s="33" t="s">
         <v>431</v>
@@ -20246,7 +20376,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="E23" s="33" t="s">
         <v>433</v>
@@ -20269,7 +20399,7 @@
         <v>18</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="E24" s="24" t="s">
         <v>434</v>
@@ -20292,7 +20422,7 @@
         <v>18</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="E25" s="24" t="s">
         <v>436</v>
@@ -20315,7 +20445,7 @@
         <v>18</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="E26" s="24" t="s">
         <v>437</v>
@@ -20338,7 +20468,7 @@
         <v>18</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="E27" s="24" t="s">
         <v>439</v>
@@ -20361,7 +20491,7 @@
         <v>18</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="E28" s="24">
         <v>160289</v>
@@ -20384,7 +20514,7 @@
         <v>18</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="E29" s="24">
         <v>160290</v>
@@ -20407,16 +20537,16 @@
         <v>18</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="E30" s="24">
         <v>160396</v>
       </c>
       <c r="F30" s="17" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>1005</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>1006</v>
       </c>
     </row>
   </sheetData>
@@ -20426,28 +20556,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <TaxCatchAll xmlns="9cf85ca5-4acf-45da-adaa-d6bfc34b6c9f" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2595f96f-d2aa-4fa4-b5ed-10baae53ecb9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BD1EFD7F07544F4C8A5DF6ACE5557D0F" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0a46465e297c47d8b88a71685f887e65">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="2595f96f-d2aa-4fa4-b5ed-10baae53ecb9" xmlns:ns3="9cf85ca5-4acf-45da-adaa-d6bfc34b6c9f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4503a5f252426d71f93d44927b16e869" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -20693,10 +20801,44 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <TaxCatchAll xmlns="9cf85ca5-4acf-45da-adaa-d6bfc34b6c9f" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2595f96f-d2aa-4fa4-b5ed-10baae53ecb9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D590CCA9-7961-4660-BBC6-10104A0DDFD4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F11AB0D6-FBA0-4F11-8778-05A9ADBB93A5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="2595f96f-d2aa-4fa4-b5ed-10baae53ecb9"/>
+    <ds:schemaRef ds:uri="9cf85ca5-4acf-45da-adaa-d6bfc34b6c9f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -20720,21 +20862,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F11AB0D6-FBA0-4F11-8778-05A9ADBB93A5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D590CCA9-7961-4660-BBC6-10104A0DDFD4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="2595f96f-d2aa-4fa4-b5ed-10baae53ecb9"/>
-    <ds:schemaRef ds:uri="9cf85ca5-4acf-45da-adaa-d6bfc34b6c9f"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Error Inventory/API Error Consolidated List.xlsx
+++ b/Error Inventory/API Error Consolidated List.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eagnmnwbp130a.usa.dce.usps.gov\VDIProfiles$\fsbtg0\Documents\API Consolidated file to upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usps365-my.sharepoint.com/personal/norman_negron-munoz_usps_gov/Documents/Documents/EMAS API/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F53487B-9017-4953-8EAD-F36B8AB737A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EEC637CC-2ACF-49A4-B5A4-20E89772DFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="13785" firstSheet="9" activeTab="10" xr2:uid="{BD4CA92B-BD2B-408A-B66B-5389FE5197CE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="13920" firstSheet="3" activeTab="4" xr2:uid="{BD4CA92B-BD2B-408A-B66B-5389FE5197CE}"/>
   </bookViews>
   <sheets>
     <sheet name="General Errors" sheetId="9" r:id="rId1"/>
@@ -34,7 +34,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Addresses!$A$1:$G$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Carrier Pickup'!$A$1:$G$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Domestic Labels Outbound'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Domestic Prices'!$A$1:$G$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Domestic Prices'!$A$1:$G$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'General Errors'!$A$1:$D$82</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'International Prices'!$A$1:$G$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">Tracking!$A$1:$G$6</definedName>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4075" uniqueCount="1019">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4187" uniqueCount="1043">
   <si>
     <t>API</t>
   </si>
@@ -3148,6 +3148,78 @@
   </si>
   <si>
     <t>destinationEntryFacilityType must be 'DESTINATION_DELIVERY_UNIT' when processingCategory is 'MIXED'</t>
+  </si>
+  <si>
+    <t>imiType can only be IMI_STD unless imageInfo.labelType is IMI_DATA_ONLY</t>
+  </si>
+  <si>
+    <t>indiciaDescription</t>
+  </si>
+  <si>
+    <t>indiciaID not found</t>
+  </si>
+  <si>
+    <t>indiciaID</t>
+  </si>
+  <si>
+    <t>030025</t>
+  </si>
+  <si>
+    <t>030026</t>
+  </si>
+  <si>
+    <t>030027</t>
+  </si>
+  <si>
+    <t>030028</t>
+  </si>
+  <si>
+    <t>030029</t>
+  </si>
+  <si>
+    <t>030030</t>
+  </si>
+  <si>
+    <t>030031</t>
+  </si>
+  <si>
+    <t>030032</t>
+  </si>
+  <si>
+    <t>030033</t>
+  </si>
+  <si>
+    <t>A minimum item value greater than 500 is required for this extra service.</t>
+  </si>
+  <si>
+    <t>Provided weight exceeds maximum allowed for First Class Postcards.</t>
+  </si>
+  <si>
+    <t>Provided dimensions do not meet minimum allowed for First Class Postcards.</t>
+  </si>
+  <si>
+    <t>Provided dimensions exceed maximum allowed for First Class Postcards.</t>
+  </si>
+  <si>
+    <t>You must have a valid province code when requesting Delivery Duties pricing for %.</t>
+  </si>
+  <si>
+    <t>One or more extra services are not available for international pieces in this price group.  (Based on the mailClass, countryCode, and rateIndicator.)</t>
+  </si>
+  <si>
+    <t>DDP is not available for the provided country and product options.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The provided invoice date is not supported. The earliest supported date is </t>
+  </si>
+  <si>
+    <t>The provided API Agreement Type is not supported.</t>
+  </si>
+  <si>
+    <t>extraServiceCodes</t>
+  </si>
+  <si>
+    <t>date</t>
   </si>
 </sst>
 </file>
@@ -3291,7 +3363,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -3431,6 +3503,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Accent1" xfId="1" builtinId="29"/>
@@ -8118,7 +8192,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:G235"/>
+  <dimension ref="A1:G237"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
@@ -13523,6 +13597,52 @@
       </c>
       <c r="G235" s="2" t="s">
         <v>1011</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7">
+      <c r="A236" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B236" s="20">
+        <v>400</v>
+      </c>
+      <c r="C236" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D236" s="50" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E236" s="17">
+        <v>160408</v>
+      </c>
+      <c r="F236" s="17" t="s">
+        <v>1020</v>
+      </c>
+      <c r="G236" s="49" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7">
+      <c r="A237" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B237" s="20">
+        <v>400</v>
+      </c>
+      <c r="C237" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D237" s="50" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E237" s="17">
+        <v>160409</v>
+      </c>
+      <c r="F237" s="17" t="s">
+        <v>1022</v>
+      </c>
+      <c r="G237" s="49" t="s">
+        <v>1021</v>
       </c>
     </row>
   </sheetData>
@@ -17959,7 +18079,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.5703125" style="10" bestFit="1" customWidth="1"/>
@@ -18573,7 +18693,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" ht="30">
       <c r="A28" s="10" t="s">
         <v>415</v>
       </c>
@@ -18583,20 +18703,20 @@
       <c r="C28" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D28" s="10" t="s">
-        <v>968</v>
+      <c r="D28" s="11" t="s">
+        <v>966</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>468</v>
+        <v>1023</v>
       </c>
       <c r="F28" s="33" t="s">
-        <v>804</v>
-      </c>
-      <c r="G28" s="11" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>810</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="30">
       <c r="A29" s="10" t="s">
         <v>415</v>
       </c>
@@ -18606,20 +18726,20 @@
       <c r="C29" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D29" s="10" t="s">
-        <v>968</v>
+      <c r="D29" s="11" t="s">
+        <v>966</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>469</v>
+        <v>1024</v>
       </c>
       <c r="F29" s="33" t="s">
-        <v>805</v>
-      </c>
-      <c r="G29" s="11" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>764</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="30">
       <c r="A30" s="10" t="s">
         <v>415</v>
       </c>
@@ -18629,20 +18749,20 @@
       <c r="C30" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D30" s="17" t="s">
-        <v>968</v>
-      </c>
-      <c r="E30" s="33" t="s">
-        <v>430</v>
+      <c r="D30" s="11" t="s">
+        <v>966</v>
+      </c>
+      <c r="E30" s="24" t="s">
+        <v>1025</v>
       </c>
       <c r="F30" s="33" t="s">
         <v>801</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="30">
       <c r="A31" s="10" t="s">
         <v>415</v>
       </c>
@@ -18652,20 +18772,20 @@
       <c r="C31" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D31" s="17" t="s">
-        <v>968</v>
-      </c>
-      <c r="E31" s="33" t="s">
-        <v>431</v>
-      </c>
-      <c r="F31" s="41" t="s">
-        <v>802</v>
+      <c r="D31" s="11" t="s">
+        <v>966</v>
+      </c>
+      <c r="E31" s="24" t="s">
+        <v>1026</v>
+      </c>
+      <c r="F31" s="33" t="s">
+        <v>801</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="30">
       <c r="A32" s="10" t="s">
         <v>415</v>
       </c>
@@ -18675,20 +18795,18 @@
       <c r="C32" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D32" s="17" t="s">
-        <v>968</v>
-      </c>
-      <c r="E32" s="33" t="s">
-        <v>433</v>
-      </c>
-      <c r="F32" s="41" t="s">
-        <v>803</v>
-      </c>
+      <c r="D32" s="11" t="s">
+        <v>966</v>
+      </c>
+      <c r="E32" s="24" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F32" s="33"/>
       <c r="G32" s="10" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="30">
       <c r="A33" s="10" t="s">
         <v>415</v>
       </c>
@@ -18698,20 +18816,20 @@
       <c r="C33" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D33" s="17" t="s">
-        <v>968</v>
+      <c r="D33" s="11" t="s">
+        <v>966</v>
       </c>
       <c r="E33" s="24" t="s">
-        <v>434</v>
-      </c>
-      <c r="F33" s="37" t="s">
-        <v>804</v>
+        <v>1028</v>
+      </c>
+      <c r="F33" s="33" t="s">
+        <v>1041</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="30">
       <c r="A34" s="10" t="s">
         <v>415</v>
       </c>
@@ -18721,20 +18839,18 @@
       <c r="C34" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D34" s="17" t="s">
-        <v>968</v>
+      <c r="D34" s="11" t="s">
+        <v>966</v>
       </c>
       <c r="E34" s="24" t="s">
-        <v>436</v>
-      </c>
-      <c r="F34" s="37" t="s">
-        <v>805</v>
-      </c>
+        <v>1029</v>
+      </c>
+      <c r="F34" s="33"/>
       <c r="G34" s="10" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="30">
       <c r="A35" s="10" t="s">
         <v>415</v>
       </c>
@@ -18744,20 +18860,20 @@
       <c r="C35" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D35" s="17" t="s">
-        <v>968</v>
+      <c r="D35" s="11" t="s">
+        <v>966</v>
       </c>
       <c r="E35" s="24" t="s">
-        <v>437</v>
-      </c>
-      <c r="F35" s="37" t="s">
-        <v>806</v>
+        <v>1030</v>
+      </c>
+      <c r="F35" s="33" t="s">
+        <v>1042</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="30">
       <c r="A36" s="10" t="s">
         <v>415</v>
       </c>
@@ -18767,20 +18883,18 @@
       <c r="C36" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D36" s="17" t="s">
-        <v>968</v>
+      <c r="D36" s="11" t="s">
+        <v>966</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>439</v>
-      </c>
-      <c r="F36" s="37" t="s">
-        <v>807</v>
-      </c>
+        <v>1031</v>
+      </c>
+      <c r="F36" s="33"/>
       <c r="G36" s="10" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="30">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" s="10" t="s">
         <v>415</v>
       </c>
@@ -18793,17 +18907,17 @@
       <c r="D37" s="10" t="s">
         <v>968</v>
       </c>
-      <c r="E37" s="24">
-        <v>160289</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>808</v>
-      </c>
-      <c r="G37" s="22" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="30">
+      <c r="E37" s="24" t="s">
+        <v>468</v>
+      </c>
+      <c r="F37" s="33" t="s">
+        <v>804</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" s="10" t="s">
         <v>415</v>
       </c>
@@ -18816,17 +18930,17 @@
       <c r="D38" s="10" t="s">
         <v>968</v>
       </c>
-      <c r="E38" s="24">
-        <v>160290</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>809</v>
-      </c>
-      <c r="G38" s="22" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="30">
+      <c r="E38" s="24" t="s">
+        <v>469</v>
+      </c>
+      <c r="F38" s="33" t="s">
+        <v>805</v>
+      </c>
+      <c r="G38" s="11" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" s="10" t="s">
         <v>415</v>
       </c>
@@ -18836,21 +18950,228 @@
       <c r="C39" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D39" s="17" t="s">
         <v>968</v>
       </c>
-      <c r="E39" s="24">
+      <c r="E39" s="33" t="s">
+        <v>430</v>
+      </c>
+      <c r="F39" s="33" t="s">
+        <v>801</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="B40" s="10">
+        <v>400</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>968</v>
+      </c>
+      <c r="E40" s="33" t="s">
+        <v>431</v>
+      </c>
+      <c r="F40" s="41" t="s">
+        <v>802</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="B41" s="10">
+        <v>400</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>968</v>
+      </c>
+      <c r="E41" s="33" t="s">
+        <v>433</v>
+      </c>
+      <c r="F41" s="41" t="s">
+        <v>803</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="B42" s="10">
+        <v>400</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>968</v>
+      </c>
+      <c r="E42" s="24" t="s">
+        <v>434</v>
+      </c>
+      <c r="F42" s="37" t="s">
+        <v>804</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="B43" s="10">
+        <v>400</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D43" s="17" t="s">
+        <v>968</v>
+      </c>
+      <c r="E43" s="24" t="s">
+        <v>436</v>
+      </c>
+      <c r="F43" s="37" t="s">
+        <v>805</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="B44" s="10">
+        <v>400</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" s="17" t="s">
+        <v>968</v>
+      </c>
+      <c r="E44" s="24" t="s">
+        <v>437</v>
+      </c>
+      <c r="F44" s="37" t="s">
+        <v>806</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="B45" s="10">
+        <v>400</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D45" s="17" t="s">
+        <v>968</v>
+      </c>
+      <c r="E45" s="24" t="s">
+        <v>439</v>
+      </c>
+      <c r="F45" s="37" t="s">
+        <v>807</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="30">
+      <c r="A46" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="B46" s="10">
+        <v>400</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>968</v>
+      </c>
+      <c r="E46" s="24">
+        <v>160289</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="G46" s="22" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="30">
+      <c r="A47" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="B47" s="10">
+        <v>400</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>968</v>
+      </c>
+      <c r="E47" s="24">
+        <v>160290</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="G47" s="22" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="30">
+      <c r="A48" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="B48" s="10">
+        <v>400</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>968</v>
+      </c>
+      <c r="E48" s="24">
         <v>160306</v>
       </c>
-      <c r="F39" s="37" t="s">
+      <c r="F48" s="37" t="s">
         <v>710</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="G48" s="2" t="s">
         <v>688</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G39" xr:uid="{E9D67488-3AD8-4C63-B43B-F8AB72C087A6}"/>
+  <autoFilter ref="A1:G48" xr:uid="{E9D67488-3AD8-4C63-B43B-F8AB72C087A6}"/>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -19864,7 +20185,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.28515625" style="2" customWidth="1"/>
@@ -20273,7 +20594,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="11" customFormat="1" ht="30">
+    <row r="19" spans="1:7" s="11" customFormat="1">
       <c r="A19" s="11" t="s">
         <v>521</v>
       </c>
@@ -20283,7 +20604,7 @@
       <c r="C19" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="50" t="s">
         <v>970</v>
       </c>
       <c r="E19" s="24" t="s">
@@ -20296,7 +20617,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="60">
+    <row r="20" spans="1:7" ht="35.25" customHeight="1">
       <c r="A20" s="11" t="s">
         <v>521</v>
       </c>
@@ -20319,7 +20640,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" ht="30">
       <c r="A21" s="11" t="s">
         <v>521</v>
       </c>
@@ -20329,17 +20650,17 @@
       <c r="C21" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D21" t="s">
-        <v>972</v>
-      </c>
-      <c r="E21" s="33" t="s">
-        <v>430</v>
-      </c>
-      <c r="F21" s="40" t="s">
-        <v>801</v>
+      <c r="D21" s="11" t="s">
+        <v>970</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F21" s="33" t="s">
+        <v>810</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>252</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="30">
@@ -20353,16 +20674,16 @@
         <v>18</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>972</v>
-      </c>
-      <c r="E22" s="33" t="s">
-        <v>431</v>
-      </c>
-      <c r="F22" s="40" t="s">
-        <v>802</v>
+        <v>970</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F22" s="33" t="s">
+        <v>764</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>432</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="30">
@@ -20376,16 +20697,16 @@
         <v>18</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>972</v>
-      </c>
-      <c r="E23" s="33" t="s">
-        <v>433</v>
-      </c>
-      <c r="F23" s="40" t="s">
-        <v>803</v>
+        <v>970</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F23" s="33" t="s">
+        <v>801</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>432</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="30">
@@ -20399,16 +20720,16 @@
         <v>18</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>434</v>
-      </c>
-      <c r="F24" s="17" t="s">
-        <v>804</v>
+        <v>1026</v>
+      </c>
+      <c r="F24" s="33" t="s">
+        <v>801</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>435</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="30">
@@ -20422,16 +20743,14 @@
         <v>18</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>436</v>
-      </c>
-      <c r="F25" s="17" t="s">
-        <v>805</v>
-      </c>
+        <v>1027</v>
+      </c>
+      <c r="F25" s="33"/>
       <c r="G25" s="10" t="s">
-        <v>435</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="30">
@@ -20445,16 +20764,16 @@
         <v>18</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>437</v>
-      </c>
-      <c r="F26" s="17" t="s">
-        <v>806</v>
+        <v>1028</v>
+      </c>
+      <c r="F26" s="33" t="s">
+        <v>1041</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>438</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="30">
@@ -20468,16 +20787,14 @@
         <v>18</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>439</v>
-      </c>
-      <c r="F27" s="17" t="s">
-        <v>807</v>
-      </c>
+        <v>1029</v>
+      </c>
+      <c r="F27" s="33"/>
       <c r="G27" s="10" t="s">
-        <v>350</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="30">
@@ -20491,16 +20808,16 @@
         <v>18</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>972</v>
-      </c>
-      <c r="E28" s="24">
-        <v>160289</v>
-      </c>
-      <c r="F28" s="37" t="s">
-        <v>808</v>
+        <v>970</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F28" s="33" t="s">
+        <v>1042</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>665</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="30">
@@ -20514,19 +20831,17 @@
         <v>18</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>972</v>
-      </c>
-      <c r="E29" s="24">
-        <v>160290</v>
-      </c>
-      <c r="F29" s="37" t="s">
-        <v>809</v>
-      </c>
+        <v>970</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F29" s="33"/>
       <c r="G29" s="10" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="30">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" s="11" t="s">
         <v>521</v>
       </c>
@@ -20536,16 +20851,223 @@
       <c r="C30" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D30" t="s">
         <v>972</v>
       </c>
-      <c r="E30" s="24">
+      <c r="E30" s="33" t="s">
+        <v>430</v>
+      </c>
+      <c r="F30" s="40" t="s">
+        <v>801</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="30">
+      <c r="A31" s="11" t="s">
+        <v>521</v>
+      </c>
+      <c r="B31" s="11">
+        <v>400</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>972</v>
+      </c>
+      <c r="E31" s="33" t="s">
+        <v>431</v>
+      </c>
+      <c r="F31" s="40" t="s">
+        <v>802</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="30">
+      <c r="A32" s="11" t="s">
+        <v>521</v>
+      </c>
+      <c r="B32" s="11">
+        <v>400</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>972</v>
+      </c>
+      <c r="E32" s="33" t="s">
+        <v>433</v>
+      </c>
+      <c r="F32" s="40" t="s">
+        <v>803</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="30">
+      <c r="A33" s="11" t="s">
+        <v>521</v>
+      </c>
+      <c r="B33" s="11">
+        <v>400</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>972</v>
+      </c>
+      <c r="E33" s="24" t="s">
+        <v>434</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>804</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="30">
+      <c r="A34" s="11" t="s">
+        <v>521</v>
+      </c>
+      <c r="B34" s="11">
+        <v>400</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>972</v>
+      </c>
+      <c r="E34" s="24" t="s">
+        <v>436</v>
+      </c>
+      <c r="F34" s="17" t="s">
+        <v>805</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="30">
+      <c r="A35" s="11" t="s">
+        <v>521</v>
+      </c>
+      <c r="B35" s="11">
+        <v>400</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>972</v>
+      </c>
+      <c r="E35" s="24" t="s">
+        <v>437</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>806</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="30">
+      <c r="A36" s="11" t="s">
+        <v>521</v>
+      </c>
+      <c r="B36" s="11">
+        <v>400</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>972</v>
+      </c>
+      <c r="E36" s="24" t="s">
+        <v>439</v>
+      </c>
+      <c r="F36" s="17" t="s">
+        <v>807</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="30">
+      <c r="A37" s="11" t="s">
+        <v>521</v>
+      </c>
+      <c r="B37" s="11">
+        <v>400</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>972</v>
+      </c>
+      <c r="E37" s="24">
+        <v>160289</v>
+      </c>
+      <c r="F37" s="37" t="s">
+        <v>808</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="30">
+      <c r="A38" s="11" t="s">
+        <v>521</v>
+      </c>
+      <c r="B38" s="11">
+        <v>400</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>972</v>
+      </c>
+      <c r="E38" s="24">
+        <v>160290</v>
+      </c>
+      <c r="F38" s="37" t="s">
+        <v>809</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="30">
+      <c r="A39" s="11" t="s">
+        <v>521</v>
+      </c>
+      <c r="B39" s="11">
+        <v>400</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>972</v>
+      </c>
+      <c r="E39" s="24">
         <v>160396</v>
       </c>
-      <c r="F30" s="17" t="s">
+      <c r="F39" s="17" t="s">
         <v>1004</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G39" s="2" t="s">
         <v>1005</v>
       </c>
     </row>
@@ -20556,6 +21078,19 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <TaxCatchAll xmlns="9cf85ca5-4acf-45da-adaa-d6bfc34b6c9f" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2595f96f-d2aa-4fa4-b5ed-10baae53ecb9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BD1EFD7F07544F4C8A5DF6ACE5557D0F" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0a46465e297c47d8b88a71685f887e65">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="2595f96f-d2aa-4fa4-b5ed-10baae53ecb9" xmlns:ns3="9cf85ca5-4acf-45da-adaa-d6bfc34b6c9f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4503a5f252426d71f93d44927b16e869" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -20801,19 +21336,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <TaxCatchAll xmlns="9cf85ca5-4acf-45da-adaa-d6bfc34b6c9f" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2595f96f-d2aa-4fa4-b5ed-10baae53ecb9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -20824,6 +21346,24 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3DC8D4E-C199-4BF9-AF5D-F16C7D7041E1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2595f96f-d2aa-4fa4-b5ed-10baae53ecb9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="9cf85ca5-4acf-45da-adaa-d6bfc34b6c9f"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F11AB0D6-FBA0-4F11-8778-05A9ADBB93A5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20843,24 +21383,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3DC8D4E-C199-4BF9-AF5D-F16C7D7041E1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2595f96f-d2aa-4fa4-b5ed-10baae53ecb9"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="9cf85ca5-4acf-45da-adaa-d6bfc34b6c9f"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D590CCA9-7961-4660-BBC6-10104A0DDFD4}">
   <ds:schemaRefs>

--- a/Error Inventory/API Error Consolidated List.xlsx
+++ b/Error Inventory/API Error Consolidated List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usps365-my.sharepoint.com/personal/norman_negron-munoz_usps_gov/Documents/Documents/EMAS API/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eagnmnwbp130a.usa.dce.usps.gov\VDIProfiles$\fsbtg0\Documents\API Consolidated file to upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EEC637CC-2ACF-49A4-B5A4-20E89772DFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A03FF57B-47E3-4436-9AB2-1F81EE5C8058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="13920" firstSheet="3" activeTab="4" xr2:uid="{BD4CA92B-BD2B-408A-B66B-5389FE5197CE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="13920" activeTab="4" xr2:uid="{BD4CA92B-BD2B-408A-B66B-5389FE5197CE}"/>
   </bookViews>
   <sheets>
     <sheet name="General Errors" sheetId="9" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4187" uniqueCount="1043">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4235" uniqueCount="1045">
   <si>
     <t>API</t>
   </si>
@@ -3220,6 +3220,12 @@
   </si>
   <si>
     <t>date</t>
+  </si>
+  <si>
+    <t>Default address: The address you entered was found but more information is needed (such as an apartment, suite, or box number) to match to a specific address.</t>
+  </si>
+  <si>
+    <t>010007</t>
   </si>
 </sst>
 </file>
@@ -3363,7 +3369,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -3504,7 +3510,6 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Accent1" xfId="1" builtinId="29"/>
@@ -7244,12 +7249,28 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="5"/>
+    <row r="8" spans="1:7" ht="75">
+      <c r="A8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="19">
+        <v>400</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>858</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>1043</v>
+      </c>
     </row>
     <row r="9" spans="1:7">
       <c r="B9" s="7"/>
@@ -8192,7 +8213,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:G237"/>
+  <dimension ref="A1:G244"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
@@ -13609,7 +13630,7 @@
       <c r="C236" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="D236" s="50" t="s">
+      <c r="D236" t="s">
         <v>1003</v>
       </c>
       <c r="E236" s="17">
@@ -13632,7 +13653,7 @@
       <c r="C237" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="D237" s="50" t="s">
+      <c r="D237" t="s">
         <v>1003</v>
       </c>
       <c r="E237" s="17">
@@ -13643,6 +13664,167 @@
       </c>
       <c r="G237" s="49" t="s">
         <v>1021</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" ht="30">
+      <c r="A238" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B238" s="20">
+        <v>400</v>
+      </c>
+      <c r="C238" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D238" s="21" t="s">
+        <v>958</v>
+      </c>
+      <c r="E238" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="F238" s="27" t="s">
+        <v>858</v>
+      </c>
+      <c r="G238" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7">
+      <c r="A239" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B239" s="20">
+        <v>400</v>
+      </c>
+      <c r="C239" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D239" s="21" t="s">
+        <v>958</v>
+      </c>
+      <c r="E239" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="F239" s="27" t="s">
+        <v>855</v>
+      </c>
+      <c r="G239" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7">
+      <c r="A240" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B240" s="20">
+        <v>400</v>
+      </c>
+      <c r="C240" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D240" s="21" t="s">
+        <v>958</v>
+      </c>
+      <c r="E240" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="F240" s="27" t="s">
+        <v>856</v>
+      </c>
+      <c r="G240" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7">
+      <c r="A241" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B241" s="20">
+        <v>400</v>
+      </c>
+      <c r="C241" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D241" s="21" t="s">
+        <v>958</v>
+      </c>
+      <c r="E241" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F241" s="27" t="s">
+        <v>857</v>
+      </c>
+      <c r="G241" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" ht="30">
+      <c r="A242" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B242" s="20">
+        <v>400</v>
+      </c>
+      <c r="C242" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D242" s="21" t="s">
+        <v>958</v>
+      </c>
+      <c r="E242" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="F242" s="27" t="s">
+        <v>858</v>
+      </c>
+      <c r="G242" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" ht="30">
+      <c r="A243" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B243" s="20">
+        <v>400</v>
+      </c>
+      <c r="C243" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D243" s="21" t="s">
+        <v>958</v>
+      </c>
+      <c r="E243" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="F243" s="27" t="s">
+        <v>858</v>
+      </c>
+      <c r="G243" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" ht="30">
+      <c r="A244" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B244" s="20">
+        <v>400</v>
+      </c>
+      <c r="C244" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D244" s="21" t="s">
+        <v>958</v>
+      </c>
+      <c r="E244" s="27" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F244" s="27" t="s">
+        <v>858</v>
+      </c>
+      <c r="G244" s="5" t="s">
+        <v>1043</v>
       </c>
     </row>
   </sheetData>
@@ -20604,7 +20786,7 @@
       <c r="C19" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="50" t="s">
+      <c r="D19" t="s">
         <v>970</v>
       </c>
       <c r="E19" s="24" t="s">
@@ -21078,19 +21260,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <TaxCatchAll xmlns="9cf85ca5-4acf-45da-adaa-d6bfc34b6c9f" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2595f96f-d2aa-4fa4-b5ed-10baae53ecb9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BD1EFD7F07544F4C8A5DF6ACE5557D0F" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0a46465e297c47d8b88a71685f887e65">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="2595f96f-d2aa-4fa4-b5ed-10baae53ecb9" xmlns:ns3="9cf85ca5-4acf-45da-adaa-d6bfc34b6c9f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4503a5f252426d71f93d44927b16e869" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -21336,7 +21505,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -21345,25 +21514,20 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3DC8D4E-C199-4BF9-AF5D-F16C7D7041E1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2595f96f-d2aa-4fa4-b5ed-10baae53ecb9"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="9cf85ca5-4acf-45da-adaa-d6bfc34b6c9f"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <TaxCatchAll xmlns="9cf85ca5-4acf-45da-adaa-d6bfc34b6c9f" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2595f96f-d2aa-4fa4-b5ed-10baae53ecb9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F11AB0D6-FBA0-4F11-8778-05A9ADBB93A5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21383,10 +21547,28 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D590CCA9-7961-4660-BBC6-10104A0DDFD4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3DC8D4E-C199-4BF9-AF5D-F16C7D7041E1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2595f96f-d2aa-4fa4-b5ed-10baae53ecb9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="9cf85ca5-4acf-45da-adaa-d6bfc34b6c9f"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
